--- a/research/traditional_assets/database/data/netherlands/netherlands_oilfield_svcs_equip.xlsx
+++ b/research/traditional_assets/database/data/netherlands/netherlands_oilfield_svcs_equip.xlsx
@@ -1403,7 +1403,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1540,22 +1540,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.08041004605482543</v>
+        <v>0.08023597813600399</v>
       </c>
       <c r="C2">
-        <v>11228.40619148473</v>
+        <v>11119.73853136467</v>
       </c>
       <c r="D2">
-        <v>10585.40619148473</v>
+        <v>10606.89253136467</v>
       </c>
       <c r="E2">
-        <v>-9914</v>
+        <v>-9783.846</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>130.154</v>
       </c>
       <c r="G2">
         <v>643</v>
@@ -1576,28 +1576,28 @@
         <v>1486.333333333333</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>6.546746199999999</v>
       </c>
       <c r="N2">
-        <v>1486.333333333333</v>
+        <v>1479.786587133333</v>
       </c>
       <c r="O2">
-        <v>383.474</v>
+        <v>381.7849394804</v>
       </c>
       <c r="P2">
-        <v>1102.859333333333</v>
+        <v>1098.001647652933</v>
       </c>
       <c r="Q2">
-        <v>1137.859333333333</v>
+        <v>1133.001647652933</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.08041004605482543</v>
+        <v>0.08066944660202423</v>
       </c>
       <c r="T2">
-        <v>0.7993082229751833</v>
+        <v>0.8052989977372801</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1614,7 +1614,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>227.0339017164486</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1622,22 +1622,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.08023597813600399</v>
+        <v>0.08006191021718252</v>
       </c>
       <c r="C3">
-        <v>11119.73853136467</v>
+        <v>11011.15827493717</v>
       </c>
       <c r="D3">
-        <v>10606.89253136467</v>
+        <v>10628.46627493717</v>
       </c>
       <c r="E3">
-        <v>-9783.846</v>
+        <v>-9653.691999999999</v>
       </c>
       <c r="F3">
-        <v>130.154</v>
+        <v>260.308</v>
       </c>
       <c r="G3">
         <v>643</v>
@@ -1658,28 +1658,28 @@
         <v>1486.333333333333</v>
       </c>
       <c r="M3">
-        <v>6.546746199999999</v>
+        <v>13.0934924</v>
       </c>
       <c r="N3">
-        <v>1479.786587133333</v>
+        <v>1473.239840933333</v>
       </c>
       <c r="O3">
-        <v>381.7849394804</v>
+        <v>380.0958789608</v>
       </c>
       <c r="P3">
-        <v>1098.001647652933</v>
+        <v>1093.143961972533</v>
       </c>
       <c r="Q3">
-        <v>1133.001647652933</v>
+        <v>1128.143961972533</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.08066944660202423</v>
+        <v>0.08093414103794136</v>
       </c>
       <c r="T3">
-        <v>0.8052989977372801</v>
+        <v>0.8114120332088075</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1696,7 +1696,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>227.0339017164486</v>
+        <v>113.5169508582243</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1704,22 +1704,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.08006191021718252</v>
+        <v>0.07988784229836109</v>
       </c>
       <c r="C4">
-        <v>11011.15827493717</v>
+        <v>10902.66595660979</v>
       </c>
       <c r="D4">
-        <v>10628.46627493717</v>
+        <v>10650.12795660979</v>
       </c>
       <c r="E4">
-        <v>-9653.691999999999</v>
+        <v>-9523.538</v>
       </c>
       <c r="F4">
-        <v>260.308</v>
+        <v>390.462</v>
       </c>
       <c r="G4">
         <v>643</v>
@@ -1740,28 +1740,28 @@
         <v>1486.333333333333</v>
       </c>
       <c r="M4">
-        <v>13.0934924</v>
+        <v>19.6402386</v>
       </c>
       <c r="N4">
-        <v>1473.239840933333</v>
+        <v>1466.693094733333</v>
       </c>
       <c r="O4">
-        <v>380.0958789608</v>
+        <v>378.4068184412</v>
       </c>
       <c r="P4">
-        <v>1093.143961972533</v>
+        <v>1088.286276292133</v>
       </c>
       <c r="Q4">
-        <v>1128.143961972533</v>
+        <v>1123.286276292133</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.08093414103794136</v>
+        <v>0.08120429309109391</v>
       </c>
       <c r="T4">
-        <v>0.8114120332088075</v>
+        <v>0.81765111064882</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1778,7 +1778,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>113.5169508582243</v>
+        <v>75.67796723881619</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1786,22 +1786,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.07988784229836109</v>
+        <v>0.07971377437953964</v>
       </c>
       <c r="C5">
-        <v>10902.66595660979</v>
+        <v>10794.26211515568</v>
       </c>
       <c r="D5">
-        <v>10650.12795660979</v>
+        <v>10671.87811515568</v>
       </c>
       <c r="E5">
-        <v>-9523.538</v>
+        <v>-9393.384</v>
       </c>
       <c r="F5">
-        <v>390.462</v>
+        <v>520.616</v>
       </c>
       <c r="G5">
         <v>643</v>
@@ -1822,28 +1822,28 @@
         <v>1486.333333333333</v>
       </c>
       <c r="M5">
-        <v>19.6402386</v>
+        <v>26.1869848</v>
       </c>
       <c r="N5">
-        <v>1466.693094733333</v>
+        <v>1460.146348533333</v>
       </c>
       <c r="O5">
-        <v>378.4068184412</v>
+        <v>376.7177579216</v>
       </c>
       <c r="P5">
-        <v>1088.286276292133</v>
+        <v>1083.428590611733</v>
       </c>
       <c r="Q5">
-        <v>1123.286276292133</v>
+        <v>1118.428590611733</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.08120429309109391</v>
+        <v>0.08148007331202045</v>
       </c>
       <c r="T5">
-        <v>0.81765111064882</v>
+        <v>0.8240201688688328</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1860,7 +1860,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>75.67796723881619</v>
+        <v>56.75847542911215</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1868,22 +1868,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.07971377437953964</v>
+        <v>0.07953970646071817</v>
       </c>
       <c r="C6">
-        <v>10794.26211515568</v>
+        <v>10685.94729375821</v>
       </c>
       <c r="D6">
-        <v>10671.87811515568</v>
+        <v>10693.71729375821</v>
       </c>
       <c r="E6">
-        <v>-9393.384</v>
+        <v>-9263.23</v>
       </c>
       <c r="F6">
-        <v>520.616</v>
+        <v>650.77</v>
       </c>
       <c r="G6">
         <v>643</v>
@@ -1904,28 +1904,28 @@
         <v>1486.333333333333</v>
       </c>
       <c r="M6">
-        <v>26.1869848</v>
+        <v>32.733731</v>
       </c>
       <c r="N6">
-        <v>1460.146348533333</v>
+        <v>1453.599602333333</v>
       </c>
       <c r="O6">
-        <v>376.7177579216</v>
+        <v>375.028697402</v>
       </c>
       <c r="P6">
-        <v>1083.428590611733</v>
+        <v>1078.570904931333</v>
       </c>
       <c r="Q6">
-        <v>1118.428590611733</v>
+        <v>1113.570904931333</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.08148007331202045</v>
+        <v>0.08176165943233493</v>
       </c>
       <c r="T6">
-        <v>0.8240201688688328</v>
+        <v>0.8305233125250564</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1942,7 +1942,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>56.75847542911215</v>
+        <v>45.40678034328972</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1950,22 +1950,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.07953970646071817</v>
+        <v>0.07936563854189674</v>
       </c>
       <c r="C7">
-        <v>10685.94729375821</v>
+        <v>10577.7220400562</v>
       </c>
       <c r="D7">
-        <v>10693.71729375821</v>
+        <v>10715.6460400562</v>
       </c>
       <c r="E7">
-        <v>-9263.23</v>
+        <v>-9133.075999999999</v>
       </c>
       <c r="F7">
-        <v>650.77</v>
+        <v>780.9240000000001</v>
       </c>
       <c r="G7">
         <v>643</v>
@@ -1986,28 +1986,28 @@
         <v>1486.333333333333</v>
       </c>
       <c r="M7">
-        <v>32.733731</v>
+        <v>39.2804772</v>
       </c>
       <c r="N7">
-        <v>1453.599602333333</v>
+        <v>1447.052856133333</v>
       </c>
       <c r="O7">
-        <v>375.028697402</v>
+        <v>373.3396368824</v>
       </c>
       <c r="P7">
-        <v>1078.570904931333</v>
+        <v>1073.713219250933</v>
       </c>
       <c r="Q7">
-        <v>1113.570904931333</v>
+        <v>1108.713219250933</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.08176165943233493</v>
+        <v>0.08204923674669866</v>
       </c>
       <c r="T7">
-        <v>0.8305233125250564</v>
+        <v>0.8371648209399228</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -2024,7 +2024,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>45.40678034328972</v>
+        <v>37.8389836194081</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2032,22 +2032,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.07936563854189674</v>
+        <v>0.0791915706230753</v>
       </c>
       <c r="C8">
-        <v>10577.7220400562</v>
+        <v>10469.58690618968</v>
       </c>
       <c r="D8">
-        <v>10715.6460400562</v>
+        <v>10737.66490618968</v>
       </c>
       <c r="E8">
-        <v>-9133.076000000001</v>
+        <v>-9002.922</v>
       </c>
       <c r="F8">
-        <v>780.924</v>
+        <v>911.0779999999999</v>
       </c>
       <c r="G8">
         <v>643</v>
@@ -2068,28 +2068,28 @@
         <v>1486.333333333333</v>
       </c>
       <c r="M8">
-        <v>39.2804772</v>
+        <v>45.82722339999999</v>
       </c>
       <c r="N8">
-        <v>1447.052856133333</v>
+        <v>1440.506109933333</v>
       </c>
       <c r="O8">
-        <v>373.3396368824</v>
+        <v>371.6505763627999</v>
       </c>
       <c r="P8">
-        <v>1073.713219250933</v>
+        <v>1068.855533570533</v>
       </c>
       <c r="Q8">
-        <v>1108.713219250933</v>
+        <v>1103.855533570533</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.08204923674669866</v>
+        <v>0.0823429985194358</v>
       </c>
       <c r="T8">
-        <v>0.8371648209399228</v>
+        <v>0.8439491574927436</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -2106,7 +2106,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>37.8389836194081</v>
+        <v>32.43341453092123</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2114,22 +2114,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.07919157062307529</v>
+        <v>0.07901750270425384</v>
       </c>
       <c r="C9">
-        <v>10469.58690618968</v>
+        <v>10361.54244884628</v>
       </c>
       <c r="D9">
-        <v>10737.66490618968</v>
+        <v>10759.77444884628</v>
       </c>
       <c r="E9">
-        <v>-9002.922</v>
+        <v>-8872.768</v>
       </c>
       <c r="F9">
-        <v>911.0780000000001</v>
+        <v>1041.232</v>
       </c>
       <c r="G9">
         <v>643</v>
@@ -2150,28 +2150,28 @@
         <v>1486.333333333333</v>
       </c>
       <c r="M9">
-        <v>45.8272234</v>
+        <v>52.3739696</v>
       </c>
       <c r="N9">
-        <v>1440.506109933333</v>
+        <v>1433.959363733333</v>
       </c>
       <c r="O9">
-        <v>371.6505763627999</v>
+        <v>369.9615158432</v>
       </c>
       <c r="P9">
-        <v>1068.855533570533</v>
+        <v>1063.997847890133</v>
       </c>
       <c r="Q9">
-        <v>1103.855533570533</v>
+        <v>1098.997847890133</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.0823429985194358</v>
+        <v>0.08264314641766721</v>
       </c>
       <c r="T9">
-        <v>0.8439491574927436</v>
+        <v>0.8508809796227994</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2188,7 +2188,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>32.43341453092123</v>
+        <v>28.37923771455608</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2196,22 +2196,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.07901750270425384</v>
+        <v>0.07884343478543239</v>
       </c>
       <c r="C10">
-        <v>10361.54244884628</v>
+        <v>10253.58922930809</v>
       </c>
       <c r="D10">
-        <v>10759.77444884628</v>
+        <v>10781.97522930809</v>
       </c>
       <c r="E10">
-        <v>-8872.768</v>
+        <v>-8742.614</v>
       </c>
       <c r="F10">
-        <v>1041.232</v>
+        <v>1171.386</v>
       </c>
       <c r="G10">
         <v>643</v>
@@ -2232,28 +2232,28 @@
         <v>1486.333333333333</v>
       </c>
       <c r="M10">
-        <v>52.3739696</v>
+        <v>58.9207158</v>
       </c>
       <c r="N10">
-        <v>1433.959363733333</v>
+        <v>1427.412617533333</v>
       </c>
       <c r="O10">
-        <v>369.9615158432</v>
+        <v>368.2724553236</v>
       </c>
       <c r="P10">
-        <v>1063.997847890133</v>
+        <v>1059.140162209733</v>
       </c>
       <c r="Q10">
-        <v>1098.997847890133</v>
+        <v>1094.140162209733</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.08264314641766721</v>
+        <v>0.08294989097300262</v>
       </c>
       <c r="T10">
-        <v>0.8508809796227994</v>
+        <v>0.8579651494919776</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2270,7 +2270,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>28.37923771455608</v>
+        <v>25.2259890796054</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2278,22 +2278,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.07884343478543239</v>
+        <v>0.07866936686661094</v>
       </c>
       <c r="C11">
-        <v>10253.58922930809</v>
+        <v>10145.72781349919</v>
       </c>
       <c r="D11">
-        <v>10781.97522930809</v>
+        <v>10804.26781349919</v>
       </c>
       <c r="E11">
-        <v>-8742.614</v>
+        <v>-8612.459999999999</v>
       </c>
       <c r="F11">
-        <v>1171.386</v>
+        <v>1301.54</v>
       </c>
       <c r="G11">
         <v>643</v>
@@ -2314,28 +2314,28 @@
         <v>1486.333333333333</v>
       </c>
       <c r="M11">
-        <v>58.9207158</v>
+        <v>65.467462</v>
       </c>
       <c r="N11">
-        <v>1427.412617533333</v>
+        <v>1420.865871333333</v>
       </c>
       <c r="O11">
-        <v>368.2724553236</v>
+        <v>366.583394804</v>
       </c>
       <c r="P11">
-        <v>1059.140162209733</v>
+        <v>1054.282476529333</v>
       </c>
       <c r="Q11">
-        <v>1094.140162209733</v>
+        <v>1089.282476529333</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.08294989097300262</v>
+        <v>0.08326345207401216</v>
       </c>
       <c r="T11">
-        <v>0.8579651494919776</v>
+        <v>0.8652067453582485</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2352,7 +2352,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>25.2259890796054</v>
+        <v>22.70339017164486</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2360,22 +2360,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.07866936686661094</v>
+        <v>0.07849529894778949</v>
       </c>
       <c r="C12">
-        <v>10145.72781349919</v>
+        <v>10037.95877203371</v>
       </c>
       <c r="D12">
-        <v>10804.26781349919</v>
+        <v>10826.65277203371</v>
       </c>
       <c r="E12">
-        <v>-8612.459999999999</v>
+        <v>-8482.306</v>
       </c>
       <c r="F12">
-        <v>1301.54</v>
+        <v>1431.694</v>
       </c>
       <c r="G12">
         <v>643</v>
@@ -2396,28 +2396,28 @@
         <v>1486.333333333333</v>
       </c>
       <c r="M12">
-        <v>65.467462</v>
+        <v>72.0142082</v>
       </c>
       <c r="N12">
-        <v>1420.865871333333</v>
+        <v>1414.319125133333</v>
       </c>
       <c r="O12">
-        <v>366.583394804</v>
+        <v>364.8943342844</v>
       </c>
       <c r="P12">
-        <v>1054.282476529333</v>
+        <v>1049.424790848933</v>
       </c>
       <c r="Q12">
-        <v>1089.282476529333</v>
+        <v>1084.424790848933</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.08326345207401216</v>
+        <v>0.0835840594918983</v>
       </c>
       <c r="T12">
-        <v>0.8652067453582485</v>
+        <v>0.8726110737158962</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2434,7 +2434,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>22.70339017164486</v>
+        <v>20.63944561058624</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2442,22 +2442,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.07849529894778949</v>
+        <v>0.07832123102896804</v>
       </c>
       <c r="C13">
-        <v>10037.95877203371</v>
+        <v>9930.282680264556</v>
       </c>
       <c r="D13">
-        <v>10826.65277203371</v>
+        <v>10849.13068026456</v>
       </c>
       <c r="E13">
-        <v>-8482.306</v>
+        <v>-8352.152</v>
       </c>
       <c r="F13">
-        <v>1431.694</v>
+        <v>1561.848</v>
       </c>
       <c r="G13">
         <v>643</v>
@@ -2478,28 +2478,28 @@
         <v>1486.333333333333</v>
       </c>
       <c r="M13">
-        <v>72.0142082</v>
+        <v>78.5609544</v>
       </c>
       <c r="N13">
-        <v>1414.319125133333</v>
+        <v>1407.772378933333</v>
       </c>
       <c r="O13">
-        <v>364.8943342844</v>
+        <v>363.2052737648</v>
       </c>
       <c r="P13">
-        <v>1049.424790848933</v>
+        <v>1044.567105168533</v>
       </c>
       <c r="Q13">
-        <v>1084.424790848933</v>
+        <v>1079.567105168533</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.0835840594918983</v>
+        <v>0.08391195344200914</v>
       </c>
       <c r="T13">
-        <v>0.8726110737158962</v>
+        <v>0.8801836822634906</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2516,7 +2516,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>20.63944561058624</v>
+        <v>18.91949180970405</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2524,22 +2524,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.07832123102896804</v>
+        <v>0.07814716311014659</v>
       </c>
       <c r="C14">
-        <v>9930.282680264556</v>
+        <v>9822.700118332676</v>
       </c>
       <c r="D14">
-        <v>10849.13068026456</v>
+        <v>10871.70211833268</v>
       </c>
       <c r="E14">
-        <v>-8352.152</v>
+        <v>-8221.998</v>
       </c>
       <c r="F14">
-        <v>1561.848</v>
+        <v>1692.002</v>
       </c>
       <c r="G14">
         <v>643</v>
@@ -2560,28 +2560,28 @@
         <v>1486.333333333333</v>
       </c>
       <c r="M14">
-        <v>78.5609544</v>
+        <v>85.10770059999999</v>
       </c>
       <c r="N14">
-        <v>1407.772378933333</v>
+        <v>1401.225632733333</v>
       </c>
       <c r="O14">
-        <v>363.2052737648</v>
+        <v>361.5162132452</v>
       </c>
       <c r="P14">
-        <v>1044.567105168533</v>
+        <v>1039.709419488133</v>
       </c>
       <c r="Q14">
-        <v>1079.567105168533</v>
+        <v>1074.709419488133</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.08391195344200914</v>
+        <v>0.08424738518407654</v>
       </c>
       <c r="T14">
-        <v>0.8801836822634906</v>
+        <v>0.887930373766202</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2598,7 +2598,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>18.91949180970405</v>
+        <v>17.46414628588066</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2606,22 +2606,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.07814716311014659</v>
+        <v>0.07797309519132516</v>
       </c>
       <c r="C15">
-        <v>9822.700118332676</v>
+        <v>9715.211671216972</v>
       </c>
       <c r="D15">
-        <v>10871.70211833268</v>
+        <v>10894.36767121697</v>
       </c>
       <c r="E15">
-        <v>-8221.998</v>
+        <v>-8091.844</v>
       </c>
       <c r="F15">
-        <v>1692.002</v>
+        <v>1822.156</v>
       </c>
       <c r="G15">
         <v>643</v>
@@ -2642,28 +2642,28 @@
         <v>1486.333333333333</v>
       </c>
       <c r="M15">
-        <v>85.10770059999999</v>
+        <v>91.6544468</v>
       </c>
       <c r="N15">
-        <v>1401.225632733333</v>
+        <v>1394.678886533333</v>
       </c>
       <c r="O15">
-        <v>361.5162132452</v>
+        <v>359.8271527256</v>
       </c>
       <c r="P15">
-        <v>1039.709419488133</v>
+        <v>1034.851733807733</v>
       </c>
       <c r="Q15">
-        <v>1074.709419488133</v>
+        <v>1069.851733807733</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.08424738518407654</v>
+        <v>0.08459061766433157</v>
       </c>
       <c r="T15">
-        <v>0.887930373766202</v>
+        <v>0.8958572208852555</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2680,7 +2680,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>17.46414628588066</v>
+        <v>16.21670726546061</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2688,22 +2688,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.07797309519132516</v>
+        <v>0.07779902727250369</v>
       </c>
       <c r="C16">
-        <v>9715.211671216972</v>
+        <v>9607.817928784854</v>
       </c>
       <c r="D16">
-        <v>10894.36767121697</v>
+        <v>10917.12792878485</v>
       </c>
       <c r="E16">
-        <v>-8091.844</v>
+        <v>-7961.69</v>
       </c>
       <c r="F16">
-        <v>1822.156</v>
+        <v>1952.31</v>
       </c>
       <c r="G16">
         <v>643</v>
@@ -2724,28 +2724,28 @@
         <v>1486.333333333333</v>
       </c>
       <c r="M16">
-        <v>91.6544468</v>
+        <v>98.201193</v>
       </c>
       <c r="N16">
-        <v>1394.678886533333</v>
+        <v>1388.132140333333</v>
       </c>
       <c r="O16">
-        <v>359.8271527256</v>
+        <v>358.138092206</v>
       </c>
       <c r="P16">
-        <v>1034.851733807733</v>
+        <v>1029.994048127333</v>
       </c>
       <c r="Q16">
-        <v>1069.851733807733</v>
+        <v>1064.994048127333</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.08459061766433157</v>
+        <v>0.08494192620294552</v>
       </c>
       <c r="T16">
-        <v>0.8958572208852555</v>
+        <v>0.9039705820541691</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2762,7 +2762,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>16.21670726546061</v>
+        <v>15.13559344776324</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2770,22 +2770,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.07779902727250369</v>
+        <v>0.07762495935368223</v>
       </c>
       <c r="C17">
-        <v>9607.817928784854</v>
+        <v>9500.51948584339</v>
       </c>
       <c r="D17">
-        <v>10917.12792878485</v>
+        <v>10939.98348584339</v>
       </c>
       <c r="E17">
-        <v>-7961.690000000001</v>
+        <v>-7831.536</v>
       </c>
       <c r="F17">
-        <v>1952.31</v>
+        <v>2082.464</v>
       </c>
       <c r="G17">
         <v>643</v>
@@ -2806,28 +2806,28 @@
         <v>1486.333333333333</v>
       </c>
       <c r="M17">
-        <v>98.20119299999999</v>
+        <v>104.7479392</v>
       </c>
       <c r="N17">
-        <v>1388.132140333333</v>
+        <v>1381.585394133333</v>
       </c>
       <c r="O17">
-        <v>358.138092206</v>
+        <v>356.4490316864</v>
       </c>
       <c r="P17">
-        <v>1029.994048127333</v>
+        <v>1025.136362446933</v>
       </c>
       <c r="Q17">
-        <v>1064.994048127333</v>
+        <v>1060.136362446933</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.08494192620294552</v>
+        <v>0.08530159923057409</v>
       </c>
       <c r="T17">
-        <v>0.9039705820541691</v>
+        <v>0.9122771184890093</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2844,7 +2844,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>15.13559344776324</v>
+        <v>14.18961885727804</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2852,22 +2852,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.07762495935368223</v>
+        <v>0.07745089143486081</v>
       </c>
       <c r="C18">
-        <v>9500.51948584339</v>
+        <v>9393.31694219113</v>
       </c>
       <c r="D18">
-        <v>10939.98348584339</v>
+        <v>10962.93494219113</v>
       </c>
       <c r="E18">
-        <v>-7831.536</v>
+        <v>-7701.382</v>
       </c>
       <c r="F18">
-        <v>2082.464</v>
+        <v>2212.618</v>
       </c>
       <c r="G18">
         <v>643</v>
@@ -2888,28 +2888,28 @@
         <v>1486.333333333333</v>
       </c>
       <c r="M18">
-        <v>104.7479392</v>
+        <v>111.2946854</v>
       </c>
       <c r="N18">
-        <v>1381.585394133333</v>
+        <v>1375.038647933333</v>
       </c>
       <c r="O18">
-        <v>356.4490316864</v>
+        <v>354.7599711668</v>
       </c>
       <c r="P18">
-        <v>1025.136362446933</v>
+        <v>1020.278676766533</v>
       </c>
       <c r="Q18">
-        <v>1060.136362446933</v>
+        <v>1055.278676766533</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.08530159923057409</v>
+        <v>0.08566993907814555</v>
       </c>
       <c r="T18">
-        <v>0.9122771184890093</v>
+        <v>0.9207838124283034</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2926,7 +2926,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>14.18961885727804</v>
+        <v>13.35493539508521</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2934,22 +2934,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.07745089143486081</v>
+        <v>0.07747716351603934</v>
       </c>
       <c r="C19">
-        <v>9393.31694219113</v>
+        <v>9259.692708956027</v>
       </c>
       <c r="D19">
-        <v>10962.93494219113</v>
+        <v>10959.46470895603</v>
       </c>
       <c r="E19">
-        <v>-7701.382</v>
+        <v>-7571.227999999999</v>
       </c>
       <c r="F19">
-        <v>2212.618</v>
+        <v>2342.772</v>
       </c>
       <c r="G19">
         <v>643</v>
@@ -2970,45 +2970,45 @@
         <v>1486.333333333333</v>
       </c>
       <c r="M19">
-        <v>111.2946854</v>
+        <v>121.3555896</v>
       </c>
       <c r="N19">
-        <v>1375.038647933333</v>
+        <v>1364.977743733333</v>
       </c>
       <c r="O19">
-        <v>354.7599711668</v>
+        <v>352.1642578832</v>
       </c>
       <c r="P19">
-        <v>1020.278676766533</v>
+        <v>1012.813485850133</v>
       </c>
       <c r="Q19">
-        <v>1055.278676766533</v>
+        <v>1047.813485850133</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.08566993907814555</v>
+        <v>0.08604726282443823</v>
       </c>
       <c r="T19">
-        <v>0.9207838124283034</v>
+        <v>0.9294979867075802</v>
       </c>
       <c r="U19">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V19">
         <v>0.258</v>
       </c>
       <c r="W19">
-        <v>0.0373226</v>
+        <v>0.0384356</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y19">
-        <v>13.35493539508521</v>
+        <v>12.24775338517521</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -3016,22 +3016,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.07747716351603935</v>
+        <v>0.0773142255972179</v>
       </c>
       <c r="C20">
-        <v>9259.692708956027</v>
+        <v>9151.096402454445</v>
       </c>
       <c r="D20">
-        <v>10959.46470895603</v>
+        <v>10981.02240245444</v>
       </c>
       <c r="E20">
-        <v>-7571.228</v>
+        <v>-7441.074000000001</v>
       </c>
       <c r="F20">
-        <v>2342.772</v>
+        <v>2472.926</v>
       </c>
       <c r="G20">
         <v>643</v>
@@ -3052,28 +3052,28 @@
         <v>1486.333333333333</v>
       </c>
       <c r="M20">
-        <v>121.3555896</v>
+        <v>128.0975668</v>
       </c>
       <c r="N20">
-        <v>1364.977743733333</v>
+        <v>1358.235766533333</v>
       </c>
       <c r="O20">
-        <v>352.1642578832</v>
+        <v>350.4248277656</v>
       </c>
       <c r="P20">
-        <v>1012.813485850133</v>
+        <v>1007.810938767733</v>
       </c>
       <c r="Q20">
-        <v>1047.813485850133</v>
+        <v>1042.810938767733</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.08604726282443823</v>
+        <v>0.08643390320644184</v>
       </c>
       <c r="T20">
-        <v>0.9294979867075802</v>
+        <v>0.9384273257838763</v>
       </c>
       <c r="U20">
         <v>0.0518</v>
@@ -3090,7 +3090,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>12.24775338517521</v>
+        <v>11.60313478595546</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3098,22 +3098,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.0773142255972179</v>
+        <v>0.07715128767839646</v>
       </c>
       <c r="C21">
-        <v>9151.096402454445</v>
+        <v>9042.585072749303</v>
       </c>
       <c r="D21">
-        <v>10981.02240245444</v>
+        <v>11002.6650727493</v>
       </c>
       <c r="E21">
-        <v>-7441.074000000001</v>
+        <v>-7310.92</v>
       </c>
       <c r="F21">
-        <v>2472.926</v>
+        <v>2603.08</v>
       </c>
       <c r="G21">
         <v>643</v>
@@ -3134,28 +3134,28 @@
         <v>1486.333333333333</v>
       </c>
       <c r="M21">
-        <v>128.0975668</v>
+        <v>134.839544</v>
       </c>
       <c r="N21">
-        <v>1358.235766533333</v>
+        <v>1351.493789333333</v>
       </c>
       <c r="O21">
-        <v>350.4248277656</v>
+        <v>348.685397648</v>
       </c>
       <c r="P21">
-        <v>1007.810938767733</v>
+        <v>1002.808391685333</v>
       </c>
       <c r="Q21">
-        <v>1042.810938767733</v>
+        <v>1037.808391685333</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.08643390320644184</v>
+        <v>0.08683020959799556</v>
       </c>
       <c r="T21">
-        <v>0.9384273257838763</v>
+        <v>0.9475798983370799</v>
       </c>
       <c r="U21">
         <v>0.0518</v>
@@ -3172,7 +3172,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>11.60313478595546</v>
+        <v>11.02297804665769</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3180,22 +3180,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.07715128767839646</v>
+        <v>0.076988349759575</v>
       </c>
       <c r="C22">
-        <v>9042.585072749303</v>
+        <v>8934.159223279165</v>
       </c>
       <c r="D22">
-        <v>11002.6650727493</v>
+        <v>11024.39322327916</v>
       </c>
       <c r="E22">
-        <v>-7310.92</v>
+        <v>-7180.766</v>
       </c>
       <c r="F22">
-        <v>2603.08</v>
+        <v>2733.234</v>
       </c>
       <c r="G22">
         <v>643</v>
@@ -3216,28 +3216,28 @@
         <v>1486.333333333333</v>
       </c>
       <c r="M22">
-        <v>134.839544</v>
+        <v>141.5815212</v>
       </c>
       <c r="N22">
-        <v>1351.493789333333</v>
+        <v>1344.751812133333</v>
       </c>
       <c r="O22">
-        <v>348.685397648</v>
+        <v>346.9459675304</v>
       </c>
       <c r="P22">
-        <v>1002.808391685333</v>
+        <v>997.8058446029333</v>
       </c>
       <c r="Q22">
-        <v>1037.808391685333</v>
+        <v>1032.805844602933</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.08683020959799556</v>
+        <v>0.08723654906275316</v>
       </c>
       <c r="T22">
-        <v>0.9475798983370799</v>
+        <v>0.9569641815878329</v>
       </c>
       <c r="U22">
         <v>0.0518</v>
@@ -3254,7 +3254,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>11.02297804665769</v>
+        <v>10.49807433015018</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3262,22 +3262,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.076988349759575</v>
+        <v>0.07682541184075355</v>
       </c>
       <c r="C23">
-        <v>8934.159223279165</v>
+        <v>8825.819361467238</v>
       </c>
       <c r="D23">
-        <v>11024.39322327916</v>
+        <v>11046.20736146724</v>
       </c>
       <c r="E23">
-        <v>-7180.766</v>
+        <v>-7050.612</v>
       </c>
       <c r="F23">
-        <v>2733.234</v>
+        <v>2863.388</v>
       </c>
       <c r="G23">
         <v>643</v>
@@ -3298,28 +3298,28 @@
         <v>1486.333333333333</v>
       </c>
       <c r="M23">
-        <v>141.5815212</v>
+        <v>148.3234984</v>
       </c>
       <c r="N23">
-        <v>1344.751812133333</v>
+        <v>1338.009834933333</v>
       </c>
       <c r="O23">
-        <v>346.9459675304</v>
+        <v>345.2065374127999</v>
       </c>
       <c r="P23">
-        <v>997.8058446029333</v>
+        <v>992.8032975205333</v>
       </c>
       <c r="Q23">
-        <v>1032.805844602933</v>
+        <v>1027.803297520533</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.08723654906275316</v>
+        <v>0.08765330748814557</v>
       </c>
       <c r="T23">
-        <v>0.9569641815878327</v>
+        <v>0.9665890874860409</v>
       </c>
       <c r="U23">
         <v>0.0518</v>
@@ -3336,7 +3336,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>10.49807433015018</v>
+        <v>10.02088913332517</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3344,22 +3344,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.07682541184075355</v>
+        <v>0.07695259592193208</v>
       </c>
       <c r="C24">
-        <v>8825.819361467238</v>
+        <v>8678.630567373235</v>
       </c>
       <c r="D24">
-        <v>11046.20736146724</v>
+        <v>11029.17256737323</v>
       </c>
       <c r="E24">
-        <v>-7050.612</v>
+        <v>-6920.458000000001</v>
       </c>
       <c r="F24">
-        <v>2863.388</v>
+        <v>2993.542</v>
       </c>
       <c r="G24">
         <v>643</v>
@@ -3380,45 +3380,45 @@
         <v>1486.333333333333</v>
       </c>
       <c r="M24">
-        <v>148.3234984</v>
+        <v>160.154497</v>
       </c>
       <c r="N24">
-        <v>1338.009834933333</v>
+        <v>1326.178836333333</v>
       </c>
       <c r="O24">
-        <v>345.2065374127999</v>
+        <v>342.154139774</v>
       </c>
       <c r="P24">
-        <v>992.8032975205333</v>
+        <v>984.0246965593333</v>
       </c>
       <c r="Q24">
-        <v>1027.803297520533</v>
+        <v>1019.024696559333</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.08765330748814557</v>
+        <v>0.08808089080770401</v>
       </c>
       <c r="T24">
-        <v>0.9665890874860409</v>
+        <v>0.9764639909400467</v>
       </c>
       <c r="U24">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V24">
         <v>0.258</v>
       </c>
       <c r="W24">
-        <v>0.0384356</v>
+        <v>0.039697</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y24">
-        <v>10.02088913332517</v>
+        <v>9.280621906816224</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3426,22 +3426,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.07695259592193208</v>
+        <v>0.07680227200311066</v>
       </c>
       <c r="C25">
-        <v>8678.630567373235</v>
+        <v>8568.616326809499</v>
       </c>
       <c r="D25">
-        <v>11029.17256737323</v>
+        <v>11049.3123268095</v>
       </c>
       <c r="E25">
-        <v>-6920.458000000001</v>
+        <v>-6790.304</v>
       </c>
       <c r="F25">
-        <v>2993.542</v>
+        <v>3123.696</v>
       </c>
       <c r="G25">
         <v>643</v>
@@ -3462,28 +3462,28 @@
         <v>1486.333333333333</v>
       </c>
       <c r="M25">
-        <v>160.154497</v>
+        <v>167.117736</v>
       </c>
       <c r="N25">
-        <v>1326.178836333333</v>
+        <v>1319.215597333333</v>
       </c>
       <c r="O25">
-        <v>342.154139774</v>
+        <v>340.357624112</v>
       </c>
       <c r="P25">
-        <v>984.0246965593333</v>
+        <v>978.8579732213334</v>
       </c>
       <c r="Q25">
-        <v>1019.024696559333</v>
+        <v>1013.857973221333</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.08808089080770401</v>
+        <v>0.08851972631988243</v>
       </c>
       <c r="T25">
-        <v>0.9764639909400467</v>
+        <v>0.9865987602744211</v>
       </c>
       <c r="U25">
         <v>0.0535</v>
@@ -3500,7 +3500,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>9.280621906816224</v>
+        <v>8.893929327365548</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3508,22 +3508,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.07680227200311066</v>
+        <v>0.07665194808428918</v>
       </c>
       <c r="C26">
-        <v>8568.616326809499</v>
+        <v>8458.675772993229</v>
       </c>
       <c r="D26">
-        <v>11049.3123268095</v>
+        <v>11069.52577299323</v>
       </c>
       <c r="E26">
-        <v>-6790.304</v>
+        <v>-6660.15</v>
       </c>
       <c r="F26">
-        <v>3123.696</v>
+        <v>3253.85</v>
       </c>
       <c r="G26">
         <v>643</v>
@@ -3544,28 +3544,28 @@
         <v>1486.333333333333</v>
       </c>
       <c r="M26">
-        <v>167.117736</v>
+        <v>174.080975</v>
       </c>
       <c r="N26">
-        <v>1319.215597333333</v>
+        <v>1312.252358333333</v>
       </c>
       <c r="O26">
-        <v>340.357624112</v>
+        <v>338.5611084499999</v>
       </c>
       <c r="P26">
-        <v>978.8579732213334</v>
+        <v>973.6912498833333</v>
       </c>
       <c r="Q26">
-        <v>1013.857973221333</v>
+        <v>1008.691249883333</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.08851972631988243</v>
+        <v>0.08897026411238559</v>
       </c>
       <c r="T26">
-        <v>0.9865987602744211</v>
+        <v>0.9970037901243788</v>
       </c>
       <c r="U26">
         <v>0.0535</v>
@@ -3582,7 +3582,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>8.89392932736555</v>
+        <v>8.538172154270926</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3590,22 +3590,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.07665194808428918</v>
+        <v>0.07650162416546774</v>
       </c>
       <c r="C27">
-        <v>8458.675772993229</v>
+        <v>8348.809311069872</v>
       </c>
       <c r="D27">
-        <v>11069.52577299323</v>
+        <v>11089.81331106987</v>
       </c>
       <c r="E27">
-        <v>-6660.15</v>
+        <v>-6529.996</v>
       </c>
       <c r="F27">
-        <v>3253.85</v>
+        <v>3384.004</v>
       </c>
       <c r="G27">
         <v>643</v>
@@ -3626,28 +3626,28 @@
         <v>1486.333333333333</v>
       </c>
       <c r="M27">
-        <v>174.080975</v>
+        <v>181.044214</v>
       </c>
       <c r="N27">
-        <v>1312.252358333333</v>
+        <v>1305.289119333333</v>
       </c>
       <c r="O27">
-        <v>338.5611084499999</v>
+        <v>336.764592788</v>
       </c>
       <c r="P27">
-        <v>973.6912498833333</v>
+        <v>968.5245265453333</v>
       </c>
       <c r="Q27">
-        <v>1008.691249883333</v>
+        <v>1003.524526545333</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.08897026411238559</v>
+        <v>0.08943297860198343</v>
       </c>
       <c r="T27">
-        <v>0.9970037901243788</v>
+        <v>1.007690036997308</v>
       </c>
       <c r="U27">
         <v>0.0535</v>
@@ -3664,7 +3664,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>8.538172154270926</v>
+        <v>8.209780917568199</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3672,22 +3672,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.07650162416546774</v>
+        <v>0.07635130024664631</v>
       </c>
       <c r="C28">
-        <v>8348.809311069872</v>
+        <v>8239.017349160444</v>
       </c>
       <c r="D28">
-        <v>11089.81331106987</v>
+        <v>11110.17534916044</v>
       </c>
       <c r="E28">
-        <v>-6529.996</v>
+        <v>-6399.842</v>
       </c>
       <c r="F28">
-        <v>3384.004</v>
+        <v>3514.158</v>
       </c>
       <c r="G28">
         <v>643</v>
@@ -3708,28 +3708,28 @@
         <v>1486.333333333333</v>
       </c>
       <c r="M28">
-        <v>181.044214</v>
+        <v>188.007453</v>
       </c>
       <c r="N28">
-        <v>1305.289119333333</v>
+        <v>1298.325880333333</v>
       </c>
       <c r="O28">
-        <v>336.764592788</v>
+        <v>334.968077126</v>
       </c>
       <c r="P28">
-        <v>968.5245265453333</v>
+        <v>963.3578032073333</v>
       </c>
       <c r="Q28">
-        <v>1003.524526545333</v>
+        <v>998.3578032073333</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.08943297860198343</v>
+        <v>0.08990837020088535</v>
       </c>
       <c r="T28">
-        <v>1.007690036997308</v>
+        <v>1.018669057757167</v>
       </c>
       <c r="U28">
         <v>0.0535</v>
@@ -3746,7 +3746,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>8.209780917568199</v>
+        <v>7.905714957658264</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3754,22 +3754,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.07635130024664631</v>
+        <v>0.07620097632782485</v>
       </c>
       <c r="C29">
-        <v>8239.017349160444</v>
+        <v>8129.300298388887</v>
       </c>
       <c r="D29">
-        <v>11110.17534916044</v>
+        <v>11130.61229838889</v>
       </c>
       <c r="E29">
-        <v>-6399.842</v>
+        <v>-6269.688</v>
       </c>
       <c r="F29">
-        <v>3514.158</v>
+        <v>3644.312</v>
       </c>
       <c r="G29">
         <v>643</v>
@@ -3790,28 +3790,28 @@
         <v>1486.333333333333</v>
       </c>
       <c r="M29">
-        <v>188.007453</v>
+        <v>194.970692</v>
       </c>
       <c r="N29">
-        <v>1298.325880333333</v>
+        <v>1291.362641333333</v>
       </c>
       <c r="O29">
-        <v>334.968077126</v>
+        <v>333.171561464</v>
       </c>
       <c r="P29">
-        <v>963.3578032073333</v>
+        <v>958.1910798693332</v>
       </c>
       <c r="Q29">
-        <v>998.3578032073333</v>
+        <v>993.1910798693332</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.08990837020088535</v>
+        <v>0.09039696712197896</v>
       </c>
       <c r="T29">
-        <v>1.018669057757167</v>
+        <v>1.029953051315911</v>
       </c>
       <c r="U29">
         <v>0.0535</v>
@@ -3828,7 +3828,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>7.905714957658264</v>
+        <v>7.623367994884755</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3836,22 +3836,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.07620097632782485</v>
+        <v>0.0762227964090034</v>
       </c>
       <c r="C30">
-        <v>8129.300298388887</v>
+        <v>7996.175134986433</v>
       </c>
       <c r="D30">
-        <v>11130.61229838889</v>
+        <v>11127.64113498643</v>
       </c>
       <c r="E30">
-        <v>-6269.688</v>
+        <v>-6139.534</v>
       </c>
       <c r="F30">
-        <v>3644.312</v>
+        <v>3774.466</v>
       </c>
       <c r="G30">
         <v>643</v>
@@ -3872,45 +3872,45 @@
         <v>1486.333333333333</v>
       </c>
       <c r="M30">
-        <v>194.970692</v>
+        <v>204.9535038</v>
       </c>
       <c r="N30">
-        <v>1291.362641333333</v>
+        <v>1281.379829533333</v>
       </c>
       <c r="O30">
-        <v>333.171561464</v>
+        <v>330.5959960196</v>
       </c>
       <c r="P30">
-        <v>958.1910798693332</v>
+        <v>950.7838335137332</v>
       </c>
       <c r="Q30">
-        <v>993.1910798693332</v>
+        <v>985.7838335137332</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.09039696712197896</v>
+        <v>0.09089932733662451</v>
       </c>
       <c r="T30">
-        <v>1.029953051315911</v>
+        <v>1.041554903848141</v>
       </c>
       <c r="U30">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V30">
         <v>0.258</v>
       </c>
       <c r="W30">
-        <v>0.039697</v>
+        <v>0.0402906</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y30">
-        <v>7.623367994884755</v>
+        <v>7.252051347137463</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3918,22 +3918,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.0762227964090034</v>
+        <v>0.07607840849018195</v>
       </c>
       <c r="C31">
-        <v>7996.175134986434</v>
+        <v>7885.711460272131</v>
       </c>
       <c r="D31">
-        <v>11127.64113498643</v>
+        <v>11147.33146027213</v>
       </c>
       <c r="E31">
-        <v>-6139.534000000001</v>
+        <v>-6009.38</v>
       </c>
       <c r="F31">
-        <v>3774.465999999999</v>
+        <v>3904.62</v>
       </c>
       <c r="G31">
         <v>643</v>
@@ -3954,28 +3954,28 @@
         <v>1486.333333333333</v>
       </c>
       <c r="M31">
-        <v>204.9535038</v>
+        <v>212.020866</v>
       </c>
       <c r="N31">
-        <v>1281.379829533333</v>
+        <v>1274.312467333333</v>
       </c>
       <c r="O31">
-        <v>330.5959960196</v>
+        <v>328.7726165719999</v>
       </c>
       <c r="P31">
-        <v>950.7838335137333</v>
+        <v>945.5398507613332</v>
       </c>
       <c r="Q31">
-        <v>985.7838335137333</v>
+        <v>980.5398507613332</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.09089932733662451</v>
+        <v>0.09141604070025994</v>
       </c>
       <c r="T31">
-        <v>1.041554903848141</v>
+        <v>1.053488237881292</v>
       </c>
       <c r="U31">
         <v>0.0543</v>
@@ -3992,7 +3992,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>7.252051347137465</v>
+        <v>7.010316302232881</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -4000,22 +4000,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.07607840849018195</v>
+        <v>0.07593402057136049</v>
       </c>
       <c r="C32">
-        <v>7885.711460272131</v>
+        <v>7775.317593016738</v>
       </c>
       <c r="D32">
-        <v>11147.33146027213</v>
+        <v>11167.09159301674</v>
       </c>
       <c r="E32">
-        <v>-6009.38</v>
+        <v>-5879.226000000001</v>
       </c>
       <c r="F32">
-        <v>3904.62</v>
+        <v>4034.774</v>
       </c>
       <c r="G32">
         <v>643</v>
@@ -4036,28 +4036,28 @@
         <v>1486.333333333333</v>
       </c>
       <c r="M32">
-        <v>212.020866</v>
+        <v>219.0882282</v>
       </c>
       <c r="N32">
-        <v>1274.312467333333</v>
+        <v>1267.245105133333</v>
       </c>
       <c r="O32">
-        <v>328.7726165719999</v>
+        <v>326.9492371244</v>
       </c>
       <c r="P32">
-        <v>945.5398507613332</v>
+        <v>940.2958680089332</v>
       </c>
       <c r="Q32">
-        <v>980.5398507613332</v>
+        <v>975.2958680089332</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.09141604070025994</v>
+        <v>0.09194773126284131</v>
       </c>
       <c r="T32">
-        <v>1.053488237881292</v>
+        <v>1.065767465654534</v>
       </c>
       <c r="U32">
         <v>0.0543</v>
@@ -4074,7 +4074,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>7.010316302232881</v>
+        <v>6.784177066676982</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4082,22 +4082,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.07593402057136049</v>
+        <v>0.07578963265253905</v>
       </c>
       <c r="C33">
-        <v>7775.317593016738</v>
+        <v>7664.993905108586</v>
       </c>
       <c r="D33">
-        <v>11167.09159301674</v>
+        <v>11186.92190510859</v>
       </c>
       <c r="E33">
-        <v>-5879.226000000001</v>
+        <v>-5749.072</v>
       </c>
       <c r="F33">
-        <v>4034.774</v>
+        <v>4164.928</v>
       </c>
       <c r="G33">
         <v>643</v>
@@ -4118,28 +4118,28 @@
         <v>1486.333333333333</v>
       </c>
       <c r="M33">
-        <v>219.0882282</v>
+        <v>226.1555904</v>
       </c>
       <c r="N33">
-        <v>1267.245105133333</v>
+        <v>1260.177742933333</v>
       </c>
       <c r="O33">
-        <v>326.9492371244</v>
+        <v>325.1258576768</v>
       </c>
       <c r="P33">
-        <v>940.2958680089332</v>
+        <v>935.0518852565333</v>
       </c>
       <c r="Q33">
-        <v>975.2958680089332</v>
+        <v>970.0518852565333</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.09194773126284131</v>
+        <v>0.09249505978314566</v>
       </c>
       <c r="T33">
-        <v>1.065767465654534</v>
+        <v>1.078407847185812</v>
       </c>
       <c r="U33">
         <v>0.0543</v>
@@ -4156,7 +4156,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>6.784177066676982</v>
+        <v>6.572171533343327</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4164,22 +4164,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.07578963265253905</v>
+        <v>0.0756452447337176</v>
       </c>
       <c r="C34">
-        <v>7664.993905108586</v>
+        <v>7554.740771082281</v>
       </c>
       <c r="D34">
-        <v>11186.92190510859</v>
+        <v>11206.82277108228</v>
       </c>
       <c r="E34">
-        <v>-5749.072</v>
+        <v>-5618.918</v>
       </c>
       <c r="F34">
-        <v>4164.928</v>
+        <v>4295.082</v>
       </c>
       <c r="G34">
         <v>643</v>
@@ -4200,28 +4200,28 @@
         <v>1486.333333333333</v>
       </c>
       <c r="M34">
-        <v>226.1555904</v>
+        <v>233.2229526</v>
       </c>
       <c r="N34">
-        <v>1260.177742933333</v>
+        <v>1253.110380733333</v>
       </c>
       <c r="O34">
-        <v>325.1258576768</v>
+        <v>323.3024782291999</v>
       </c>
       <c r="P34">
-        <v>935.0518852565333</v>
+        <v>929.8079025041332</v>
       </c>
       <c r="Q34">
-        <v>970.0518852565333</v>
+        <v>964.8079025041332</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.09249505978314566</v>
+        <v>0.09305872646823522</v>
       </c>
       <c r="T34">
-        <v>1.078407847185812</v>
+        <v>1.09142555353892</v>
       </c>
       <c r="U34">
         <v>0.0543</v>
@@ -4238,7 +4238,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>6.572171533343327</v>
+        <v>6.37301482021171</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4246,22 +4246,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.0756452447337176</v>
+        <v>0.07550085681489616</v>
       </c>
       <c r="C35">
-        <v>7554.740771082281</v>
+        <v>7444.558568142274</v>
       </c>
       <c r="D35">
-        <v>11206.82277108228</v>
+        <v>11226.79456814227</v>
       </c>
       <c r="E35">
-        <v>-5618.918</v>
+        <v>-5488.764</v>
       </c>
       <c r="F35">
-        <v>4295.082</v>
+        <v>4425.236</v>
       </c>
       <c r="G35">
         <v>643</v>
@@ -4282,28 +4282,28 @@
         <v>1486.333333333333</v>
       </c>
       <c r="M35">
-        <v>233.2229526</v>
+        <v>240.2903148</v>
       </c>
       <c r="N35">
-        <v>1253.110380733333</v>
+        <v>1246.043018533333</v>
       </c>
       <c r="O35">
-        <v>323.3024782291999</v>
+        <v>321.4790987816</v>
       </c>
       <c r="P35">
-        <v>929.8079025041332</v>
+        <v>924.5639197517332</v>
       </c>
       <c r="Q35">
-        <v>964.8079025041332</v>
+        <v>959.5639197517332</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.09305872646823522</v>
+        <v>0.09363947396196387</v>
       </c>
       <c r="T35">
-        <v>1.09142555353892</v>
+        <v>1.104837735842122</v>
       </c>
       <c r="U35">
         <v>0.0543</v>
@@ -4320,7 +4320,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>6.37301482021171</v>
+        <v>6.185573207852542</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4328,22 +4328,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.07550085681489616</v>
+        <v>0.0756161688960747</v>
       </c>
       <c r="C36">
-        <v>7444.558568142274</v>
+        <v>7298.448837221392</v>
       </c>
       <c r="D36">
-        <v>11226.79456814227</v>
+        <v>11210.83883722139</v>
       </c>
       <c r="E36">
-        <v>-5488.764</v>
+        <v>-5358.61</v>
       </c>
       <c r="F36">
-        <v>4425.236</v>
+        <v>4555.39</v>
       </c>
       <c r="G36">
         <v>643</v>
@@ -4364,45 +4364,45 @@
         <v>1486.333333333333</v>
       </c>
       <c r="M36">
-        <v>240.2903148</v>
+        <v>251.913067</v>
       </c>
       <c r="N36">
-        <v>1246.043018533333</v>
+        <v>1234.420266333333</v>
       </c>
       <c r="O36">
-        <v>321.4790987816</v>
+        <v>318.480428714</v>
       </c>
       <c r="P36">
-        <v>924.5639197517332</v>
+        <v>915.9398376193333</v>
       </c>
       <c r="Q36">
-        <v>959.5639197517332</v>
+        <v>950.9398376193333</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.09363947396196387</v>
+        <v>0.09423809060934571</v>
       </c>
       <c r="T36">
-        <v>1.104837735842122</v>
+        <v>1.11866260067773</v>
       </c>
       <c r="U36">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V36">
         <v>0.258</v>
       </c>
       <c r="W36">
-        <v>0.0402906</v>
+        <v>0.0410326</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y36">
-        <v>6.185573207852542</v>
+        <v>5.900183547578075</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4410,22 +4410,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.0756161688960747</v>
+        <v>0.07547920097725325</v>
       </c>
       <c r="C37">
-        <v>7298.448837221392</v>
+        <v>7187.252153122926</v>
       </c>
       <c r="D37">
-        <v>11210.83883722139</v>
+        <v>11229.79615312293</v>
       </c>
       <c r="E37">
-        <v>-5358.61</v>
+        <v>-5228.455999999999</v>
       </c>
       <c r="F37">
-        <v>4555.39</v>
+        <v>4685.544000000001</v>
       </c>
       <c r="G37">
         <v>643</v>
@@ -4446,28 +4446,28 @@
         <v>1486.333333333333</v>
       </c>
       <c r="M37">
-        <v>251.913067</v>
+        <v>259.1105832000001</v>
       </c>
       <c r="N37">
-        <v>1234.420266333333</v>
+        <v>1227.222750133333</v>
       </c>
       <c r="O37">
-        <v>318.480428714</v>
+        <v>316.6234695344</v>
       </c>
       <c r="P37">
-        <v>915.9398376193333</v>
+        <v>910.5992805989332</v>
       </c>
       <c r="Q37">
-        <v>950.9398376193333</v>
+        <v>945.5992805989332</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.09423809060934571</v>
+        <v>0.09485541402695821</v>
       </c>
       <c r="T37">
-        <v>1.11866260067773</v>
+        <v>1.132919492539451</v>
       </c>
       <c r="U37">
         <v>0.0553</v>
@@ -4484,7 +4484,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>5.900183547578075</v>
+        <v>5.736289560145349</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4492,22 +4492,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.07547920097725326</v>
+        <v>0.0753422330584318</v>
       </c>
       <c r="C38">
-        <v>7187.252153122925</v>
+        <v>7076.119690545303</v>
       </c>
       <c r="D38">
-        <v>11229.79615312292</v>
+        <v>11248.8176905453</v>
       </c>
       <c r="E38">
-        <v>-5228.456</v>
+        <v>-5098.302000000001</v>
       </c>
       <c r="F38">
-        <v>4685.544</v>
+        <v>4815.697999999999</v>
       </c>
       <c r="G38">
         <v>643</v>
@@ -4528,28 +4528,28 @@
         <v>1486.333333333333</v>
       </c>
       <c r="M38">
-        <v>259.1105832</v>
+        <v>266.3080994</v>
       </c>
       <c r="N38">
-        <v>1227.222750133333</v>
+        <v>1220.025233933333</v>
       </c>
       <c r="O38">
-        <v>316.6234695344</v>
+        <v>314.7665103548</v>
       </c>
       <c r="P38">
-        <v>910.5992805989332</v>
+        <v>905.2587235785334</v>
       </c>
       <c r="Q38">
-        <v>945.5992805989332</v>
+        <v>940.2587235785334</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.09485541402695821</v>
+        <v>0.09549233501338381</v>
       </c>
       <c r="T38">
-        <v>1.132919492539451</v>
+        <v>1.147628984142813</v>
       </c>
       <c r="U38">
         <v>0.0553</v>
@@ -4566,7 +4566,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>5.73628956014535</v>
+        <v>5.58125470716845</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4574,22 +4574,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.0753422330584318</v>
+        <v>0.07520526513961034</v>
       </c>
       <c r="C39">
-        <v>7076.119690545303</v>
+        <v>6965.051776386198</v>
       </c>
       <c r="D39">
-        <v>11248.8176905453</v>
+        <v>11267.9037763862</v>
       </c>
       <c r="E39">
-        <v>-5098.302000000001</v>
+        <v>-4968.148</v>
       </c>
       <c r="F39">
-        <v>4815.697999999999</v>
+        <v>4945.852</v>
       </c>
       <c r="G39">
         <v>643</v>
@@ -4610,28 +4610,28 @@
         <v>1486.333333333333</v>
       </c>
       <c r="M39">
-        <v>266.3080994</v>
+        <v>273.5056156</v>
       </c>
       <c r="N39">
-        <v>1220.025233933333</v>
+        <v>1212.827717733333</v>
       </c>
       <c r="O39">
-        <v>314.7665103548</v>
+        <v>312.9095511752</v>
       </c>
       <c r="P39">
-        <v>905.2587235785334</v>
+        <v>899.9181665581332</v>
       </c>
       <c r="Q39">
-        <v>940.2587235785334</v>
+        <v>934.9181665581332</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.09549233501338381</v>
+        <v>0.09614980183808121</v>
       </c>
       <c r="T39">
-        <v>1.147628984142813</v>
+        <v>1.162812975475317</v>
       </c>
       <c r="U39">
         <v>0.0553</v>
@@ -4648,7 +4648,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>5.58125470716845</v>
+        <v>5.434379583295595</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4656,22 +4656,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.07520526513961034</v>
+        <v>0.07506829722078889</v>
       </c>
       <c r="C40">
-        <v>6965.051776386198</v>
+        <v>6854.048739765675</v>
       </c>
       <c r="D40">
-        <v>11267.9037763862</v>
+        <v>11287.05473976568</v>
       </c>
       <c r="E40">
-        <v>-4968.148</v>
+        <v>-4837.994</v>
       </c>
       <c r="F40">
-        <v>4945.852</v>
+        <v>5076.006</v>
       </c>
       <c r="G40">
         <v>643</v>
@@ -4692,28 +4692,28 @@
         <v>1486.333333333333</v>
       </c>
       <c r="M40">
-        <v>273.5056156</v>
+        <v>280.7031318000001</v>
       </c>
       <c r="N40">
-        <v>1212.827717733333</v>
+        <v>1205.630201533333</v>
       </c>
       <c r="O40">
-        <v>312.9095511752</v>
+        <v>311.0525919955999</v>
       </c>
       <c r="P40">
-        <v>899.9181665581332</v>
+        <v>894.5776095377332</v>
       </c>
       <c r="Q40">
-        <v>934.9181665581332</v>
+        <v>929.5776095377332</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.09614980183808121</v>
+        <v>0.09682882495211295</v>
       </c>
       <c r="T40">
-        <v>1.162812975475317</v>
+        <v>1.178494802589214</v>
       </c>
       <c r="U40">
         <v>0.0553</v>
@@ -4730,7 +4730,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>5.434379583295595</v>
+        <v>5.295036517057246</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4738,22 +4738,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.07506829722078889</v>
+        <v>0.07493132930196746</v>
       </c>
       <c r="C41">
-        <v>6854.048739765675</v>
+        <v>6743.1109120451</v>
       </c>
       <c r="D41">
-        <v>11287.05473976568</v>
+        <v>11306.2709120451</v>
       </c>
       <c r="E41">
-        <v>-4837.994</v>
+        <v>-4707.84</v>
       </c>
       <c r="F41">
-        <v>5076.006</v>
+        <v>5206.16</v>
       </c>
       <c r="G41">
         <v>643</v>
@@ -4774,28 +4774,28 @@
         <v>1486.333333333333</v>
       </c>
       <c r="M41">
-        <v>280.7031318000001</v>
+        <v>287.900648</v>
       </c>
       <c r="N41">
-        <v>1205.630201533333</v>
+        <v>1198.432685333333</v>
       </c>
       <c r="O41">
-        <v>311.0525919955999</v>
+        <v>309.195632816</v>
       </c>
       <c r="P41">
-        <v>894.5776095377332</v>
+        <v>889.2370525173333</v>
       </c>
       <c r="Q41">
-        <v>929.5776095377332</v>
+        <v>924.2370525173333</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.09682882495211295</v>
+        <v>0.09753048216994575</v>
       </c>
       <c r="T41">
-        <v>1.178494802589214</v>
+        <v>1.194699357273574</v>
       </c>
       <c r="U41">
         <v>0.0553</v>
@@ -4812,7 +4812,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>5.295036517057246</v>
+        <v>5.162660604130815</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4820,22 +4820,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.07493132930196746</v>
+        <v>0.074794361383146</v>
       </c>
       <c r="C42">
-        <v>6743.1109120451</v>
+        <v>6632.238626846254</v>
       </c>
       <c r="D42">
-        <v>11306.2709120451</v>
+        <v>11325.55262684625</v>
       </c>
       <c r="E42">
-        <v>-4707.84</v>
+        <v>-4577.686</v>
       </c>
       <c r="F42">
-        <v>5206.16</v>
+        <v>5336.314</v>
       </c>
       <c r="G42">
         <v>643</v>
@@ -4856,28 +4856,28 @@
         <v>1486.333333333333</v>
       </c>
       <c r="M42">
-        <v>287.900648</v>
+        <v>295.0981642</v>
       </c>
       <c r="N42">
-        <v>1198.432685333333</v>
+        <v>1191.235169133333</v>
       </c>
       <c r="O42">
-        <v>309.195632816</v>
+        <v>307.3386736364</v>
       </c>
       <c r="P42">
-        <v>889.2370525173333</v>
+        <v>883.8964954969333</v>
       </c>
       <c r="Q42">
-        <v>924.2370525173333</v>
+        <v>918.8964954969333</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.09753048216994575</v>
+        <v>0.09825592437821357</v>
       </c>
       <c r="T42">
-        <v>1.194699357273574</v>
+        <v>1.211453218896387</v>
       </c>
       <c r="U42">
         <v>0.0553</v>
@@ -4894,7 +4894,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>5.162660604130815</v>
+        <v>5.036742052810552</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4902,22 +4902,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.074794361383146</v>
+        <v>0.07465739346432457</v>
       </c>
       <c r="C43">
-        <v>6632.238626846254</v>
+        <v>6521.432220070637</v>
       </c>
       <c r="D43">
-        <v>11325.55262684625</v>
+        <v>11344.90022007064</v>
       </c>
       <c r="E43">
-        <v>-4577.686</v>
+        <v>-4447.531999999999</v>
       </c>
       <c r="F43">
-        <v>5336.314</v>
+        <v>5466.468000000001</v>
       </c>
       <c r="G43">
         <v>643</v>
@@ -4938,28 +4938,28 @@
         <v>1486.333333333333</v>
       </c>
       <c r="M43">
-        <v>295.0981642</v>
+        <v>302.2956804</v>
       </c>
       <c r="N43">
-        <v>1191.235169133333</v>
+        <v>1184.037652933333</v>
       </c>
       <c r="O43">
-        <v>307.3386736364</v>
+        <v>305.4817144568</v>
       </c>
       <c r="P43">
-        <v>883.8964954969333</v>
+        <v>878.5559384765332</v>
       </c>
       <c r="Q43">
-        <v>918.8964954969333</v>
+        <v>913.5559384765332</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.09825592437821357</v>
+        <v>0.09900638183504235</v>
       </c>
       <c r="T43">
-        <v>1.211453218896387</v>
+        <v>1.228784799885504</v>
       </c>
       <c r="U43">
         <v>0.0553</v>
@@ -4976,7 +4976,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>5.036742052810552</v>
+        <v>4.916819622981729</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4984,22 +4984,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.07465739346432457</v>
+        <v>0.07452042554550312</v>
       </c>
       <c r="C44">
-        <v>6521.432220070638</v>
+        <v>6410.692029918988</v>
       </c>
       <c r="D44">
-        <v>11344.90022007064</v>
+        <v>11364.31402991899</v>
       </c>
       <c r="E44">
-        <v>-4447.532</v>
+        <v>-4317.378000000001</v>
       </c>
       <c r="F44">
-        <v>5466.468</v>
+        <v>5596.621999999999</v>
       </c>
       <c r="G44">
         <v>643</v>
@@ -5020,28 +5020,28 @@
         <v>1486.333333333333</v>
       </c>
       <c r="M44">
-        <v>302.2956804</v>
+        <v>309.4931966</v>
       </c>
       <c r="N44">
-        <v>1184.037652933333</v>
+        <v>1176.840136733333</v>
       </c>
       <c r="O44">
-        <v>305.4817144568</v>
+        <v>303.6247552772</v>
       </c>
       <c r="P44">
-        <v>878.5559384765332</v>
+        <v>873.2153814561334</v>
       </c>
       <c r="Q44">
-        <v>913.5559384765332</v>
+        <v>908.2153814561334</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.09900638183504235</v>
+        <v>0.09978317113246159</v>
       </c>
       <c r="T44">
-        <v>1.228784799885504</v>
+        <v>1.246724506523362</v>
       </c>
       <c r="U44">
         <v>0.0553</v>
@@ -5058,7 +5058,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>4.916819622981729</v>
+        <v>4.802474980586806</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5066,22 +5066,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.07452042554550312</v>
+        <v>0.07438345762668166</v>
       </c>
       <c r="C45">
-        <v>6410.692029918988</v>
+        <v>6300.018396910962</v>
       </c>
       <c r="D45">
-        <v>11364.31402991899</v>
+        <v>11383.79439691096</v>
       </c>
       <c r="E45">
-        <v>-4317.378000000001</v>
+        <v>-4187.224</v>
       </c>
       <c r="F45">
-        <v>5596.621999999999</v>
+        <v>5726.776</v>
       </c>
       <c r="G45">
         <v>643</v>
@@ -5102,28 +5102,28 @@
         <v>1486.333333333333</v>
       </c>
       <c r="M45">
-        <v>309.4931966</v>
+        <v>316.6907128</v>
       </c>
       <c r="N45">
-        <v>1176.840136733333</v>
+        <v>1169.642620533333</v>
       </c>
       <c r="O45">
-        <v>303.6247552772</v>
+        <v>301.7677960976</v>
       </c>
       <c r="P45">
-        <v>873.2153814561334</v>
+        <v>867.8748244357332</v>
       </c>
       <c r="Q45">
-        <v>908.2153814561334</v>
+        <v>902.8748244357332</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.09978317113246159</v>
+        <v>0.1005877029047887</v>
       </c>
       <c r="T45">
-        <v>1.246724506523362</v>
+        <v>1.265304916969715</v>
       </c>
       <c r="U45">
         <v>0.0553</v>
@@ -5140,7 +5140,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>4.802474980586806</v>
+        <v>4.693327821937105</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5148,22 +5148,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.07438345762668166</v>
+        <v>0.07424648970786021</v>
       </c>
       <c r="C46">
-        <v>6300.018396910962</v>
+        <v>6189.411663905074</v>
       </c>
       <c r="D46">
-        <v>11383.79439691096</v>
+        <v>11403.34166390507</v>
       </c>
       <c r="E46">
-        <v>-4187.224</v>
+        <v>-4057.07</v>
       </c>
       <c r="F46">
-        <v>5726.776</v>
+        <v>5856.93</v>
       </c>
       <c r="G46">
         <v>643</v>
@@ -5184,28 +5184,28 @@
         <v>1486.333333333333</v>
       </c>
       <c r="M46">
-        <v>316.6907128</v>
+        <v>323.888229</v>
       </c>
       <c r="N46">
-        <v>1169.642620533333</v>
+        <v>1162.445104333333</v>
       </c>
       <c r="O46">
-        <v>301.7677960976</v>
+        <v>299.910836918</v>
       </c>
       <c r="P46">
-        <v>867.8748244357332</v>
+        <v>862.5342674153333</v>
       </c>
       <c r="Q46">
-        <v>902.8748244357332</v>
+        <v>897.5342674153333</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1005877029047887</v>
+        <v>0.1014214903779276</v>
       </c>
       <c r="T46">
-        <v>1.265304916969715</v>
+        <v>1.284560978705027</v>
       </c>
       <c r="U46">
         <v>0.0553</v>
@@ -5222,7 +5222,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>4.693327821937105</v>
+        <v>4.589031648116281</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5230,22 +5230,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.07424648970786021</v>
+        <v>0.07496282178903876</v>
       </c>
       <c r="C47">
-        <v>6189.411663905074</v>
+        <v>5957.762823890166</v>
       </c>
       <c r="D47">
-        <v>11403.34166390507</v>
+        <v>11301.84682389017</v>
       </c>
       <c r="E47">
-        <v>-4057.07</v>
+        <v>-3926.916</v>
       </c>
       <c r="F47">
-        <v>5856.93</v>
+        <v>5987.084</v>
       </c>
       <c r="G47">
         <v>643</v>
@@ -5266,45 +5266,45 @@
         <v>1486.333333333333</v>
       </c>
       <c r="M47">
-        <v>323.888229</v>
+        <v>346.0534552</v>
       </c>
       <c r="N47">
-        <v>1162.445104333333</v>
+        <v>1140.279878133333</v>
       </c>
       <c r="O47">
-        <v>299.910836918</v>
+        <v>294.1922085584</v>
       </c>
       <c r="P47">
-        <v>862.5342674153333</v>
+        <v>846.0876695749332</v>
       </c>
       <c r="Q47">
-        <v>897.5342674153333</v>
+        <v>881.0876695749332</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1014214903779276</v>
+        <v>0.1022861588685903</v>
       </c>
       <c r="T47">
-        <v>1.284560978705027</v>
+        <v>1.304530227912016</v>
       </c>
       <c r="U47">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V47">
         <v>0.258</v>
       </c>
       <c r="W47">
-        <v>0.0410326</v>
+        <v>0.0428876</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y47">
-        <v>4.589031648116281</v>
+        <v>4.295097508777404</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5312,22 +5312,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.07496282178903876</v>
+        <v>0.0748444038702173</v>
       </c>
       <c r="C48">
-        <v>5957.762823890166</v>
+        <v>5844.262255355229</v>
       </c>
       <c r="D48">
-        <v>11301.84682389017</v>
+        <v>11318.50025535523</v>
       </c>
       <c r="E48">
-        <v>-3926.916</v>
+        <v>-3796.762</v>
       </c>
       <c r="F48">
-        <v>5987.084</v>
+        <v>6117.238</v>
       </c>
       <c r="G48">
         <v>643</v>
@@ -5348,28 +5348,28 @@
         <v>1486.333333333333</v>
       </c>
       <c r="M48">
-        <v>346.0534552</v>
+        <v>353.5763564000001</v>
       </c>
       <c r="N48">
-        <v>1140.279878133333</v>
+        <v>1132.756976933333</v>
       </c>
       <c r="O48">
-        <v>294.1922085584</v>
+        <v>292.2513000488</v>
       </c>
       <c r="P48">
-        <v>846.0876695749332</v>
+        <v>840.5056768845332</v>
       </c>
       <c r="Q48">
-        <v>881.0876695749332</v>
+        <v>875.5056768845332</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1022861588685903</v>
+        <v>0.1031834563589006</v>
       </c>
       <c r="T48">
-        <v>1.304530227912016</v>
+        <v>1.325253033692854</v>
       </c>
       <c r="U48">
         <v>0.0578</v>
@@ -5386,7 +5386,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>4.295097508777404</v>
+        <v>4.203712455399161</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5394,22 +5394,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.0748444038702173</v>
+        <v>0.07472598595139586</v>
       </c>
       <c r="C49">
-        <v>5844.262255355229</v>
+        <v>5730.810837378888</v>
       </c>
       <c r="D49">
-        <v>11318.50025535523</v>
+        <v>11335.20283737889</v>
       </c>
       <c r="E49">
-        <v>-3796.762</v>
+        <v>-3666.607999999999</v>
       </c>
       <c r="F49">
-        <v>6117.238</v>
+        <v>6247.392000000001</v>
       </c>
       <c r="G49">
         <v>643</v>
@@ -5430,28 +5430,28 @@
         <v>1486.333333333333</v>
       </c>
       <c r="M49">
-        <v>353.5763564000001</v>
+        <v>361.0992576</v>
       </c>
       <c r="N49">
-        <v>1132.756976933333</v>
+        <v>1125.234075733333</v>
       </c>
       <c r="O49">
-        <v>292.2513000488</v>
+        <v>290.3103915391999</v>
       </c>
       <c r="P49">
-        <v>840.5056768845332</v>
+        <v>834.9236841941332</v>
       </c>
       <c r="Q49">
-        <v>875.5056768845332</v>
+        <v>869.9236841941332</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1031834563589006</v>
+        <v>0.1041152652911459</v>
       </c>
       <c r="T49">
-        <v>1.325253033692854</v>
+        <v>1.346772870465263</v>
       </c>
       <c r="U49">
         <v>0.0578</v>
@@ -5468,7 +5468,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>4.203712455399161</v>
+        <v>4.116135112578346</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5476,22 +5476,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.07472598595139586</v>
+        <v>0.0746075680325744</v>
       </c>
       <c r="C50">
-        <v>5730.810837378889</v>
+        <v>5617.408787875483</v>
       </c>
       <c r="D50">
-        <v>11335.20283737889</v>
+        <v>11351.95478787548</v>
       </c>
       <c r="E50">
-        <v>-3666.608</v>
+        <v>-3536.454000000001</v>
       </c>
       <c r="F50">
-        <v>6247.392</v>
+        <v>6377.545999999999</v>
       </c>
       <c r="G50">
         <v>643</v>
@@ -5512,28 +5512,28 @@
         <v>1486.333333333333</v>
       </c>
       <c r="M50">
-        <v>361.0992576</v>
+        <v>368.6221588</v>
       </c>
       <c r="N50">
-        <v>1125.234075733333</v>
+        <v>1117.711174533333</v>
       </c>
       <c r="O50">
-        <v>290.3103915391999</v>
+        <v>288.3694830296</v>
       </c>
       <c r="P50">
-        <v>834.9236841941332</v>
+        <v>829.3416915037333</v>
       </c>
       <c r="Q50">
-        <v>869.9236841941332</v>
+        <v>864.3416915037333</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1041152652911459</v>
+        <v>0.1050836157501459</v>
       </c>
       <c r="T50">
-        <v>1.346772870465263</v>
+        <v>1.369136622405217</v>
       </c>
       <c r="U50">
         <v>0.0578</v>
@@ -5550,7 +5550,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>4.116135112578346</v>
+        <v>4.032132355178788</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5558,22 +5558,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.0746075680325744</v>
+        <v>0.07578765011375296</v>
       </c>
       <c r="C51">
-        <v>5617.408787875483</v>
+        <v>5322.494678185486</v>
       </c>
       <c r="D51">
-        <v>11351.95478787548</v>
+        <v>11187.19467818549</v>
       </c>
       <c r="E51">
-        <v>-3536.454000000001</v>
+        <v>-3406.3</v>
       </c>
       <c r="F51">
-        <v>6377.545999999999</v>
+        <v>6507.7</v>
       </c>
       <c r="G51">
         <v>643</v>
@@ -5594,45 +5594,45 @@
         <v>1486.333333333333</v>
       </c>
       <c r="M51">
-        <v>368.6221588</v>
+        <v>398.92201</v>
       </c>
       <c r="N51">
-        <v>1117.711174533333</v>
+        <v>1087.411323333333</v>
       </c>
       <c r="O51">
-        <v>288.3694830296</v>
+        <v>280.55212142</v>
       </c>
       <c r="P51">
-        <v>829.3416915037333</v>
+        <v>806.8592019133332</v>
       </c>
       <c r="Q51">
-        <v>864.3416915037333</v>
+        <v>841.8592019133332</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1050836157501459</v>
+        <v>0.1060907002275059</v>
       </c>
       <c r="T51">
-        <v>1.369136622405217</v>
+        <v>1.392394924422769</v>
       </c>
       <c r="U51">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V51">
         <v>0.258</v>
       </c>
       <c r="W51">
-        <v>0.0428876</v>
+        <v>0.0454846</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y51">
-        <v>4.032132355178788</v>
+        <v>3.72587447188821</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5640,22 +5640,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.07578765011375296</v>
+        <v>0.0756952021949315</v>
       </c>
       <c r="C52">
-        <v>5322.494678185486</v>
+        <v>5205.075170002709</v>
       </c>
       <c r="D52">
-        <v>11187.19467818549</v>
+        <v>11199.92917000271</v>
       </c>
       <c r="E52">
-        <v>-3406.3</v>
+        <v>-3276.146</v>
       </c>
       <c r="F52">
-        <v>6507.7</v>
+        <v>6637.854</v>
       </c>
       <c r="G52">
         <v>643</v>
@@ -5676,28 +5676,28 @@
         <v>1486.333333333333</v>
       </c>
       <c r="M52">
-        <v>398.92201</v>
+        <v>406.9004502</v>
       </c>
       <c r="N52">
-        <v>1087.411323333333</v>
+        <v>1079.432883133333</v>
       </c>
       <c r="O52">
-        <v>280.55212142</v>
+        <v>278.4936838484</v>
       </c>
       <c r="P52">
-        <v>806.8592019133332</v>
+        <v>800.9391992849332</v>
       </c>
       <c r="Q52">
-        <v>841.8592019133332</v>
+        <v>835.9391992849332</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1060907002275059</v>
+        <v>0.1071388901937378</v>
       </c>
       <c r="T52">
-        <v>1.392394924422769</v>
+        <v>1.416602544890018</v>
       </c>
       <c r="U52">
         <v>0.0613</v>
@@ -5714,7 +5714,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>3.72587447188821</v>
+        <v>3.652818109694323</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5722,22 +5722,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.0756952021949315</v>
+        <v>0.07560275427611005</v>
       </c>
       <c r="C53">
-        <v>5205.075170002709</v>
+        <v>5087.684686449156</v>
       </c>
       <c r="D53">
-        <v>11199.92917000271</v>
+        <v>11212.69268644916</v>
       </c>
       <c r="E53">
-        <v>-3276.146</v>
+        <v>-3145.992</v>
       </c>
       <c r="F53">
-        <v>6637.854</v>
+        <v>6768.008</v>
       </c>
       <c r="G53">
         <v>643</v>
@@ -5758,28 +5758,28 @@
         <v>1486.333333333333</v>
       </c>
       <c r="M53">
-        <v>406.9004502</v>
+        <v>414.8788904</v>
       </c>
       <c r="N53">
-        <v>1079.432883133333</v>
+        <v>1071.454442933333</v>
       </c>
       <c r="O53">
-        <v>278.4936838484</v>
+        <v>276.4352462768</v>
       </c>
       <c r="P53">
-        <v>800.9391992849332</v>
+        <v>795.0191966565333</v>
       </c>
       <c r="Q53">
-        <v>835.9391992849332</v>
+        <v>830.0191966565333</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1071388901937378</v>
+        <v>0.1082307547418959</v>
       </c>
       <c r="T53">
-        <v>1.416602544890018</v>
+        <v>1.441818816210068</v>
       </c>
       <c r="U53">
         <v>0.0613</v>
@@ -5796,7 +5796,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>3.652818109694323</v>
+        <v>3.582571607584817</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5804,22 +5804,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.07560275427611005</v>
+        <v>0.07551030635728861</v>
       </c>
       <c r="C54">
-        <v>5087.684686449156</v>
+        <v>4970.323326868038</v>
       </c>
       <c r="D54">
-        <v>11212.69268644916</v>
+        <v>11225.48532686804</v>
       </c>
       <c r="E54">
-        <v>-3145.992</v>
+        <v>-3015.838</v>
       </c>
       <c r="F54">
-        <v>6768.008</v>
+        <v>6898.162</v>
       </c>
       <c r="G54">
         <v>643</v>
@@ -5840,28 +5840,28 @@
         <v>1486.333333333333</v>
       </c>
       <c r="M54">
-        <v>414.8788904</v>
+        <v>422.8573306</v>
       </c>
       <c r="N54">
-        <v>1071.454442933333</v>
+        <v>1063.476002733333</v>
       </c>
       <c r="O54">
-        <v>276.4352462768</v>
+        <v>274.3768087051999</v>
       </c>
       <c r="P54">
-        <v>795.0191966565333</v>
+        <v>789.0991940281333</v>
       </c>
       <c r="Q54">
-        <v>830.0191966565333</v>
+        <v>824.0991940281333</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1082307547418959</v>
+        <v>0.1093690816112524</v>
       </c>
       <c r="T54">
-        <v>1.441818816210068</v>
+        <v>1.468108120352249</v>
       </c>
       <c r="U54">
         <v>0.0613</v>
@@ -5878,7 +5878,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>3.582571607584817</v>
+        <v>3.51497591687567</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5886,22 +5886,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.07551030635728861</v>
+        <v>0.07653976243846716</v>
       </c>
       <c r="C55">
-        <v>4970.323326868038</v>
+        <v>4699.34317819323</v>
       </c>
       <c r="D55">
-        <v>11225.48532686804</v>
+        <v>11084.65917819323</v>
       </c>
       <c r="E55">
-        <v>-3015.838</v>
+        <v>-2885.683999999999</v>
       </c>
       <c r="F55">
-        <v>6898.162</v>
+        <v>7028.316000000001</v>
       </c>
       <c r="G55">
         <v>643</v>
@@ -5922,45 +5922,45 @@
         <v>1486.333333333333</v>
       </c>
       <c r="M55">
-        <v>422.8573306</v>
+        <v>450.5150556000001</v>
       </c>
       <c r="N55">
-        <v>1063.476002733333</v>
+        <v>1035.818277733333</v>
       </c>
       <c r="O55">
-        <v>274.3768087051999</v>
+        <v>267.2411156552</v>
       </c>
       <c r="P55">
-        <v>789.0991940281333</v>
+        <v>768.5771620781331</v>
       </c>
       <c r="Q55">
-        <v>824.0991940281333</v>
+        <v>803.5771620781331</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1093690816112524</v>
+        <v>0.1105569009531895</v>
       </c>
       <c r="T55">
-        <v>1.468108120352249</v>
+        <v>1.495540437718002</v>
       </c>
       <c r="U55">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V55">
         <v>0.258</v>
       </c>
       <c r="W55">
-        <v>0.0454846</v>
+        <v>0.04756220000000001</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y55">
-        <v>3.51497591687567</v>
+        <v>3.299186819303566</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5968,22 +5968,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.07653976243846716</v>
+        <v>0.07646809051964572</v>
       </c>
       <c r="C56">
-        <v>4699.34317819323</v>
+        <v>4578.879120969924</v>
       </c>
       <c r="D56">
-        <v>11084.65917819323</v>
+        <v>11094.34912096992</v>
       </c>
       <c r="E56">
-        <v>-2885.683999999999</v>
+        <v>-2755.53</v>
       </c>
       <c r="F56">
-        <v>7028.316000000001</v>
+        <v>7158.47</v>
       </c>
       <c r="G56">
         <v>643</v>
@@ -6004,28 +6004,28 @@
         <v>1486.333333333333</v>
       </c>
       <c r="M56">
-        <v>450.5150556000001</v>
+        <v>458.8579270000001</v>
       </c>
       <c r="N56">
-        <v>1035.818277733333</v>
+        <v>1027.475406333333</v>
       </c>
       <c r="O56">
-        <v>267.2411156552</v>
+        <v>265.088654834</v>
       </c>
       <c r="P56">
-        <v>768.5771620781331</v>
+        <v>762.3867514993333</v>
       </c>
       <c r="Q56">
-        <v>803.5771620781331</v>
+        <v>797.3867514993333</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1105569009531895</v>
+        <v>0.1117975122658794</v>
       </c>
       <c r="T56">
-        <v>1.495540437718002</v>
+        <v>1.5241919691889</v>
       </c>
       <c r="U56">
         <v>0.0641</v>
@@ -6042,7 +6042,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>3.299186819303566</v>
+        <v>3.239201604407137</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6050,22 +6050,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.07646809051964572</v>
+        <v>0.07639641860082426</v>
       </c>
       <c r="C57">
-        <v>4578.879120969924</v>
+        <v>4458.43201999977</v>
       </c>
       <c r="D57">
-        <v>11094.34912096992</v>
+        <v>11104.05601999977</v>
       </c>
       <c r="E57">
-        <v>-2755.53</v>
+        <v>-2625.375999999999</v>
       </c>
       <c r="F57">
-        <v>7158.47</v>
+        <v>7288.624000000001</v>
       </c>
       <c r="G57">
         <v>643</v>
@@ -6086,28 +6086,28 @@
         <v>1486.333333333333</v>
       </c>
       <c r="M57">
-        <v>458.8579270000001</v>
+        <v>467.2007984000001</v>
       </c>
       <c r="N57">
-        <v>1027.475406333333</v>
+        <v>1019.132534933333</v>
       </c>
       <c r="O57">
-        <v>265.088654834</v>
+        <v>262.9361940128</v>
       </c>
       <c r="P57">
-        <v>762.3867514993333</v>
+        <v>756.1963409205332</v>
       </c>
       <c r="Q57">
-        <v>797.3867514993333</v>
+        <v>791.1963409205332</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1117975122658794</v>
+        <v>0.1130945150018733</v>
       </c>
       <c r="T57">
-        <v>1.5241919691889</v>
+        <v>1.554145842999384</v>
       </c>
       <c r="U57">
         <v>0.0641</v>
@@ -6124,7 +6124,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>3.239201604407137</v>
+        <v>3.181358718614153</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6132,22 +6132,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.07639641860082426</v>
+        <v>0.07632474668200281</v>
       </c>
       <c r="C58">
-        <v>4458.43201999977</v>
+        <v>4338.001919828901</v>
       </c>
       <c r="D58">
-        <v>11104.05601999977</v>
+        <v>11113.7799198289</v>
       </c>
       <c r="E58">
-        <v>-2625.375999999999</v>
+        <v>-2495.222</v>
       </c>
       <c r="F58">
-        <v>7288.624000000001</v>
+        <v>7418.778</v>
       </c>
       <c r="G58">
         <v>643</v>
@@ -6168,28 +6168,28 @@
         <v>1486.333333333333</v>
       </c>
       <c r="M58">
-        <v>467.2007984000001</v>
+        <v>475.5436698</v>
       </c>
       <c r="N58">
-        <v>1019.132534933333</v>
+        <v>1010.789663533333</v>
       </c>
       <c r="O58">
-        <v>262.9361940128</v>
+        <v>260.7837331916</v>
       </c>
       <c r="P58">
-        <v>756.1963409205332</v>
+        <v>750.0059303417331</v>
       </c>
       <c r="Q58">
-        <v>791.1963409205332</v>
+        <v>785.0059303417331</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1130945150018733</v>
+        <v>0.1144518434465182</v>
       </c>
       <c r="T58">
-        <v>1.554145842999384</v>
+        <v>1.585492920242914</v>
       </c>
       <c r="U58">
         <v>0.0641</v>
@@ -6206,7 +6206,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>3.181358718614153</v>
+        <v>3.125545407761273</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6214,22 +6214,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.07632474668200281</v>
+        <v>0.07625307476318137</v>
       </c>
       <c r="C59">
-        <v>4338.001919828901</v>
+        <v>4217.58886515962</v>
       </c>
       <c r="D59">
-        <v>11113.7799198289</v>
+        <v>11123.52086515962</v>
       </c>
       <c r="E59">
-        <v>-2495.222</v>
+        <v>-2365.067999999999</v>
       </c>
       <c r="F59">
-        <v>7418.778</v>
+        <v>7548.932000000001</v>
       </c>
       <c r="G59">
         <v>643</v>
@@ -6250,28 +6250,28 @@
         <v>1486.333333333333</v>
       </c>
       <c r="M59">
-        <v>475.5436698</v>
+        <v>483.8865412000001</v>
       </c>
       <c r="N59">
-        <v>1010.789663533333</v>
+        <v>1002.446792133333</v>
       </c>
       <c r="O59">
-        <v>260.7837331916</v>
+        <v>258.6312723704</v>
       </c>
       <c r="P59">
-        <v>750.0059303417331</v>
+        <v>743.8155197629333</v>
       </c>
       <c r="Q59">
-        <v>785.0059303417331</v>
+        <v>778.8155197629333</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1144518434465182</v>
+        <v>0.1158738065790033</v>
       </c>
       <c r="T59">
-        <v>1.585492920242914</v>
+        <v>1.618332715450421</v>
       </c>
       <c r="U59">
         <v>0.0641</v>
@@ -6288,7 +6288,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>3.125545407761273</v>
+        <v>3.071656693834354</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6296,22 +6296,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.07625307476318136</v>
+        <v>0.07618140284435991</v>
       </c>
       <c r="C60">
-        <v>4217.588865159625</v>
+        <v>4097.192900851094</v>
       </c>
       <c r="D60">
-        <v>11123.52086515962</v>
+        <v>11133.27890085109</v>
       </c>
       <c r="E60">
-        <v>-2365.068000000001</v>
+        <v>-2234.914000000001</v>
       </c>
       <c r="F60">
-        <v>7548.931999999999</v>
+        <v>7679.085999999999</v>
       </c>
       <c r="G60">
         <v>643</v>
@@ -6332,28 +6332,28 @@
         <v>1486.333333333333</v>
       </c>
       <c r="M60">
-        <v>483.8865412</v>
+        <v>492.2294126</v>
       </c>
       <c r="N60">
-        <v>1002.446792133333</v>
+        <v>994.1039207333333</v>
       </c>
       <c r="O60">
-        <v>258.6312723704</v>
+        <v>256.4788115492</v>
       </c>
       <c r="P60">
-        <v>743.8155197629333</v>
+        <v>737.6251091841333</v>
       </c>
       <c r="Q60">
-        <v>778.8155197629333</v>
+        <v>772.6251091841333</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1158738065790032</v>
+        <v>0.1173651337667315</v>
       </c>
       <c r="T60">
-        <v>1.618332715450421</v>
+        <v>1.652774451887563</v>
       </c>
       <c r="U60">
         <v>0.0641</v>
@@ -6370,7 +6370,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>3.071656693834355</v>
+        <v>3.019594715972756</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6378,22 +6378,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.07618140284435991</v>
+        <v>0.07958229092553845</v>
       </c>
       <c r="C61">
-        <v>4097.192900851094</v>
+        <v>3522.126241073056</v>
       </c>
       <c r="D61">
-        <v>11133.27890085109</v>
+        <v>10688.36624107306</v>
       </c>
       <c r="E61">
-        <v>-2234.914000000001</v>
+        <v>-2104.76</v>
       </c>
       <c r="F61">
-        <v>7679.085999999999</v>
+        <v>7809.24</v>
       </c>
       <c r="G61">
         <v>643</v>
@@ -6414,45 +6414,45 @@
         <v>1486.333333333333</v>
       </c>
       <c r="M61">
-        <v>492.2294126</v>
+        <v>561.484356</v>
       </c>
       <c r="N61">
-        <v>994.1039207333333</v>
+        <v>924.8489773333332</v>
       </c>
       <c r="O61">
-        <v>256.4788115492</v>
+        <v>238.611036152</v>
       </c>
       <c r="P61">
-        <v>737.6251091841333</v>
+        <v>686.2379411813332</v>
       </c>
       <c r="Q61">
-        <v>772.6251091841333</v>
+        <v>721.2379411813332</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1173651337667315</v>
+        <v>0.1189310273138461</v>
       </c>
       <c r="T61">
-        <v>1.652774451887563</v>
+        <v>1.688938275146562</v>
       </c>
       <c r="U61">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V61">
         <v>0.258</v>
       </c>
       <c r="W61">
-        <v>0.04756220000000001</v>
+        <v>0.0533498</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y61">
-        <v>3.019594715972756</v>
+        <v>2.647150036239537</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6460,22 +6460,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.07958229092553845</v>
+        <v>0.079568495006717</v>
       </c>
       <c r="C62">
-        <v>3522.126241073056</v>
+        <v>3393.705213691576</v>
       </c>
       <c r="D62">
-        <v>10688.36624107306</v>
+        <v>10690.09921369158</v>
       </c>
       <c r="E62">
-        <v>-2104.76</v>
+        <v>-1974.606000000001</v>
       </c>
       <c r="F62">
-        <v>7809.24</v>
+        <v>7939.393999999999</v>
       </c>
       <c r="G62">
         <v>643</v>
@@ -6496,28 +6496,28 @@
         <v>1486.333333333333</v>
       </c>
       <c r="M62">
-        <v>561.484356</v>
+        <v>570.8424285999999</v>
       </c>
       <c r="N62">
-        <v>924.8489773333332</v>
+        <v>915.4909047333333</v>
       </c>
       <c r="O62">
-        <v>238.611036152</v>
+        <v>236.1966534212</v>
       </c>
       <c r="P62">
-        <v>686.2379411813332</v>
+        <v>679.2942513121333</v>
       </c>
       <c r="Q62">
-        <v>721.2379411813332</v>
+        <v>714.2942513121333</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1189310273138461</v>
+        <v>0.1205772230941462</v>
       </c>
       <c r="T62">
-        <v>1.688938275146562</v>
+        <v>1.726956653444484</v>
       </c>
       <c r="U62">
         <v>0.07190000000000001</v>
@@ -6534,7 +6534,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>2.647150036239537</v>
+        <v>2.603754134006103</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6542,22 +6542,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.079568495006717</v>
+        <v>0.07955469908789556</v>
       </c>
       <c r="C63">
-        <v>3393.705213691576</v>
+        <v>3265.284748356912</v>
       </c>
       <c r="D63">
-        <v>10690.09921369158</v>
+        <v>10691.83274835691</v>
       </c>
       <c r="E63">
-        <v>-1974.606000000001</v>
+        <v>-1844.452</v>
       </c>
       <c r="F63">
-        <v>7939.393999999999</v>
+        <v>8069.548</v>
       </c>
       <c r="G63">
         <v>643</v>
@@ -6578,28 +6578,28 @@
         <v>1486.333333333333</v>
       </c>
       <c r="M63">
-        <v>570.8424285999999</v>
+        <v>580.2005012000001</v>
       </c>
       <c r="N63">
-        <v>915.4909047333333</v>
+        <v>906.1328321333332</v>
       </c>
       <c r="O63">
-        <v>236.1966534212</v>
+        <v>233.7822706904</v>
       </c>
       <c r="P63">
-        <v>679.2942513121333</v>
+        <v>672.3505614429332</v>
       </c>
       <c r="Q63">
-        <v>714.2942513121333</v>
+        <v>707.3505614429332</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1205772230941462</v>
+        <v>0.1223100607576199</v>
       </c>
       <c r="T63">
-        <v>1.726956653444484</v>
+        <v>1.766975999021245</v>
       </c>
       <c r="U63">
         <v>0.07190000000000001</v>
@@ -6616,7 +6616,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>2.603754134006103</v>
+        <v>2.561758099586648</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6624,22 +6624,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.07955469908789556</v>
+        <v>0.07954090316907411</v>
       </c>
       <c r="C64">
-        <v>3265.284748356912</v>
+        <v>3136.864845342538</v>
       </c>
       <c r="D64">
-        <v>10691.83274835691</v>
+        <v>10693.56684534254</v>
       </c>
       <c r="E64">
-        <v>-1844.452</v>
+        <v>-1714.298000000001</v>
       </c>
       <c r="F64">
-        <v>8069.548</v>
+        <v>8199.701999999999</v>
       </c>
       <c r="G64">
         <v>643</v>
@@ -6660,28 +6660,28 @@
         <v>1486.333333333333</v>
       </c>
       <c r="M64">
-        <v>580.2005012000001</v>
+        <v>589.5585738</v>
       </c>
       <c r="N64">
-        <v>906.1328321333332</v>
+        <v>896.7747595333333</v>
       </c>
       <c r="O64">
-        <v>233.7822706904</v>
+        <v>231.3678879596</v>
       </c>
       <c r="P64">
-        <v>672.3505614429332</v>
+        <v>665.4068715737333</v>
       </c>
       <c r="Q64">
-        <v>707.3505614429332</v>
+        <v>700.4068715737333</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1223100607576199</v>
+        <v>0.1241365653218219</v>
       </c>
       <c r="T64">
-        <v>1.766975999021245</v>
+        <v>1.809158552467019</v>
       </c>
       <c r="U64">
         <v>0.07190000000000001</v>
@@ -6698,7 +6698,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>2.561758099586648</v>
+        <v>2.521095272609083</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6706,22 +6706,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.07954090316907411</v>
+        <v>0.08137913925025267</v>
       </c>
       <c r="C65">
-        <v>3136.864845342538</v>
+        <v>2780.502317187364</v>
       </c>
       <c r="D65">
-        <v>10693.56684534254</v>
+        <v>10467.35831718736</v>
       </c>
       <c r="E65">
-        <v>-1714.298000000001</v>
+        <v>-1584.144</v>
       </c>
       <c r="F65">
-        <v>8199.701999999999</v>
+        <v>8329.856</v>
       </c>
       <c r="G65">
         <v>643</v>
@@ -6742,45 +6742,45 @@
         <v>1486.333333333333</v>
       </c>
       <c r="M65">
-        <v>589.5585738</v>
+        <v>631.4030848</v>
       </c>
       <c r="N65">
-        <v>896.7747595333333</v>
+        <v>854.9302485333333</v>
       </c>
       <c r="O65">
-        <v>231.3678879596</v>
+        <v>220.5720041216</v>
       </c>
       <c r="P65">
-        <v>665.4068715737333</v>
+        <v>634.3582444117333</v>
       </c>
       <c r="Q65">
-        <v>700.4068715737333</v>
+        <v>669.3582444117333</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1241365653218219</v>
+        <v>0.1260645423618129</v>
       </c>
       <c r="T65">
-        <v>1.809158552467019</v>
+        <v>1.853684581104225</v>
       </c>
       <c r="U65">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V65">
         <v>0.258</v>
       </c>
       <c r="W65">
-        <v>0.0533498</v>
+        <v>0.0562436</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y65">
-        <v>2.521095272609083</v>
+        <v>2.354016584832075</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6788,22 +6788,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.08137913925025267</v>
+        <v>0.0813942813314312</v>
       </c>
       <c r="C66">
-        <v>2780.502317187364</v>
+        <v>2648.524706655862</v>
       </c>
       <c r="D66">
-        <v>10467.35831718736</v>
+        <v>10465.53470665586</v>
       </c>
       <c r="E66">
-        <v>-1584.144</v>
+        <v>-1453.99</v>
       </c>
       <c r="F66">
-        <v>8329.856</v>
+        <v>8460.01</v>
       </c>
       <c r="G66">
         <v>643</v>
@@ -6824,28 +6824,28 @@
         <v>1486.333333333333</v>
       </c>
       <c r="M66">
-        <v>631.4030848</v>
+        <v>641.268758</v>
       </c>
       <c r="N66">
-        <v>854.9302485333333</v>
+        <v>845.0645753333332</v>
       </c>
       <c r="O66">
-        <v>220.5720041216</v>
+        <v>218.026660436</v>
       </c>
       <c r="P66">
-        <v>634.3582444117333</v>
+        <v>627.0379148973332</v>
       </c>
       <c r="Q66">
-        <v>669.3582444117333</v>
+        <v>662.0379148973332</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1260645423618129</v>
+        <v>0.1281026895183749</v>
       </c>
       <c r="T66">
-        <v>1.853684581104225</v>
+        <v>1.900754954234986</v>
       </c>
       <c r="U66">
         <v>0.07580000000000001</v>
@@ -6862,7 +6862,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>2.354016584832075</v>
+        <v>2.317800945065428</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6870,22 +6870,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.0813942813314312</v>
+        <v>0.08140942341260976</v>
       </c>
       <c r="C67">
-        <v>2648.524706655862</v>
+        <v>2516.547731428127</v>
       </c>
       <c r="D67">
-        <v>10465.53470665586</v>
+        <v>10463.71173142813</v>
       </c>
       <c r="E67">
-        <v>-1453.99</v>
+        <v>-1323.835999999999</v>
       </c>
       <c r="F67">
-        <v>8460.01</v>
+        <v>8590.164000000001</v>
       </c>
       <c r="G67">
         <v>643</v>
@@ -6906,28 +6906,28 @@
         <v>1486.333333333333</v>
       </c>
       <c r="M67">
-        <v>641.268758</v>
+        <v>651.1344312000001</v>
       </c>
       <c r="N67">
-        <v>845.0645753333332</v>
+        <v>835.1989021333331</v>
       </c>
       <c r="O67">
-        <v>218.026660436</v>
+        <v>215.4813167504</v>
       </c>
       <c r="P67">
-        <v>627.0379148973332</v>
+        <v>619.7175853829332</v>
       </c>
       <c r="Q67">
-        <v>662.0379148973332</v>
+        <v>654.7175853829332</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1281026895183749</v>
+        <v>0.1302607276841464</v>
       </c>
       <c r="T67">
-        <v>1.900754954234986</v>
+        <v>1.950594172844027</v>
       </c>
       <c r="U67">
         <v>0.07580000000000001</v>
@@ -6944,7 +6944,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>2.317800945065428</v>
+        <v>2.282682748928073</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6952,22 +6952,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.08140942341260976</v>
+        <v>0.08142456549378832</v>
       </c>
       <c r="C68">
-        <v>2516.547731428127</v>
+        <v>2384.571391172231</v>
       </c>
       <c r="D68">
-        <v>10463.71173142813</v>
+        <v>10461.88939117223</v>
       </c>
       <c r="E68">
-        <v>-1323.835999999999</v>
+        <v>-1193.681999999999</v>
       </c>
       <c r="F68">
-        <v>8590.164000000001</v>
+        <v>8720.318000000001</v>
       </c>
       <c r="G68">
         <v>643</v>
@@ -6988,28 +6988,28 @@
         <v>1486.333333333333</v>
       </c>
       <c r="M68">
-        <v>651.1344312000001</v>
+        <v>661.0001044000002</v>
       </c>
       <c r="N68">
-        <v>835.1989021333331</v>
+        <v>825.3332289333331</v>
       </c>
       <c r="O68">
-        <v>215.4813167504</v>
+        <v>212.9359730648</v>
       </c>
       <c r="P68">
-        <v>619.7175853829332</v>
+        <v>612.3972558685332</v>
       </c>
       <c r="Q68">
-        <v>654.7175853829332</v>
+        <v>647.3972558685332</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1302607276841464</v>
+        <v>0.1325495560417828</v>
       </c>
       <c r="T68">
-        <v>1.950594172844027</v>
+        <v>2.003453950156646</v>
       </c>
       <c r="U68">
         <v>0.07580000000000001</v>
@@ -7026,7 +7026,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>2.282682748928073</v>
+        <v>2.248612857153026</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7034,22 +7034,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.08142456549378832</v>
+        <v>0.08143970757496688</v>
       </c>
       <c r="C69">
-        <v>2384.571391172231</v>
+        <v>2252.595685556478</v>
       </c>
       <c r="D69">
-        <v>10461.88939117223</v>
+        <v>10460.06768555648</v>
       </c>
       <c r="E69">
-        <v>-1193.681999999999</v>
+        <v>-1063.528</v>
       </c>
       <c r="F69">
-        <v>8720.318000000001</v>
+        <v>8850.472</v>
       </c>
       <c r="G69">
         <v>643</v>
@@ -7070,28 +7070,28 @@
         <v>1486.333333333333</v>
       </c>
       <c r="M69">
-        <v>661.0001044000002</v>
+        <v>670.8657776</v>
       </c>
       <c r="N69">
-        <v>825.3332289333331</v>
+        <v>815.4675557333333</v>
       </c>
       <c r="O69">
-        <v>212.9359730648</v>
+        <v>210.3906293792</v>
       </c>
       <c r="P69">
-        <v>612.3972558685332</v>
+        <v>605.0769263541333</v>
       </c>
       <c r="Q69">
-        <v>647.3972558685332</v>
+        <v>640.0769263541333</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1325495560417828</v>
+        <v>0.1349814361717715</v>
       </c>
       <c r="T69">
-        <v>2.003453950156646</v>
+        <v>2.059617463551304</v>
       </c>
       <c r="U69">
         <v>0.07580000000000001</v>
@@ -7108,7 +7108,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>2.248612857153026</v>
+        <v>2.215545021018424</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7116,22 +7116,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.08143970757496688</v>
+        <v>0.08145484965614541</v>
       </c>
       <c r="C70">
-        <v>2252.595685556478</v>
+        <v>2120.620614249399</v>
       </c>
       <c r="D70">
-        <v>10460.06768555648</v>
+        <v>10458.2466142494</v>
       </c>
       <c r="E70">
-        <v>-1063.528</v>
+        <v>-933.3739999999998</v>
       </c>
       <c r="F70">
-        <v>8850.472</v>
+        <v>8980.626</v>
       </c>
       <c r="G70">
         <v>643</v>
@@ -7152,28 +7152,28 @@
         <v>1486.333333333333</v>
       </c>
       <c r="M70">
-        <v>670.8657776</v>
+        <v>680.7314508000001</v>
       </c>
       <c r="N70">
-        <v>815.4675557333333</v>
+        <v>805.6018825333332</v>
       </c>
       <c r="O70">
-        <v>210.3906293792</v>
+        <v>207.8452856936</v>
       </c>
       <c r="P70">
-        <v>605.0769263541333</v>
+        <v>597.7565968397332</v>
       </c>
       <c r="Q70">
-        <v>640.0769263541333</v>
+        <v>632.7565968397332</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1349814361717715</v>
+        <v>0.1375702117940175</v>
       </c>
       <c r="T70">
-        <v>2.059617463551304</v>
+        <v>2.119404429423037</v>
       </c>
       <c r="U70">
         <v>0.07580000000000001</v>
@@ -7190,7 +7190,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>2.215545021018424</v>
+        <v>2.183435672887722</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7198,22 +7198,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.08145484965614541</v>
+        <v>0.08146999173732397</v>
       </c>
       <c r="C71">
-        <v>2120.620614249399</v>
+        <v>1988.646176919754</v>
       </c>
       <c r="D71">
-        <v>10458.2466142494</v>
+        <v>10456.42617691975</v>
       </c>
       <c r="E71">
-        <v>-933.3739999999998</v>
+        <v>-803.2199999999993</v>
       </c>
       <c r="F71">
-        <v>8980.626</v>
+        <v>9110.780000000001</v>
       </c>
       <c r="G71">
         <v>643</v>
@@ -7234,28 +7234,28 @@
         <v>1486.333333333333</v>
       </c>
       <c r="M71">
-        <v>680.7314508000001</v>
+        <v>690.5971240000001</v>
       </c>
       <c r="N71">
-        <v>805.6018825333332</v>
+        <v>795.7362093333331</v>
       </c>
       <c r="O71">
-        <v>207.8452856936</v>
+        <v>205.299942008</v>
       </c>
       <c r="P71">
-        <v>597.7565968397332</v>
+        <v>590.4362673253331</v>
       </c>
       <c r="Q71">
-        <v>632.7565968397332</v>
+        <v>625.4362673253331</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1375702117940175</v>
+        <v>0.1403315724577466</v>
       </c>
       <c r="T71">
-        <v>2.119404429423037</v>
+        <v>2.183177193019551</v>
       </c>
       <c r="U71">
         <v>0.07580000000000001</v>
@@ -7272,7 +7272,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>2.183435672887722</v>
+        <v>2.152243734703611</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7280,22 +7280,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.08146999173732397</v>
+        <v>0.08148513381850252</v>
       </c>
       <c r="C72">
-        <v>1988.646176919754</v>
+        <v>1856.672373236539</v>
       </c>
       <c r="D72">
-        <v>10456.42617691975</v>
+        <v>10454.60637323654</v>
       </c>
       <c r="E72">
-        <v>-803.2199999999993</v>
+        <v>-673.0659999999989</v>
       </c>
       <c r="F72">
-        <v>9110.780000000001</v>
+        <v>9240.934000000001</v>
       </c>
       <c r="G72">
         <v>643</v>
@@ -7316,28 +7316,28 @@
         <v>1486.333333333333</v>
       </c>
       <c r="M72">
-        <v>690.5971240000001</v>
+        <v>700.4627972000002</v>
       </c>
       <c r="N72">
-        <v>795.7362093333331</v>
+        <v>785.8705361333331</v>
       </c>
       <c r="O72">
-        <v>205.299942008</v>
+        <v>202.7545983223999</v>
       </c>
       <c r="P72">
-        <v>590.4362673253331</v>
+        <v>583.1159378109331</v>
       </c>
       <c r="Q72">
-        <v>625.4362673253331</v>
+        <v>618.1159378109331</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1403315724577466</v>
+        <v>0.1432833717879397</v>
       </c>
       <c r="T72">
-        <v>2.183177193019551</v>
+        <v>2.251348078243412</v>
       </c>
       <c r="U72">
         <v>0.07580000000000001</v>
@@ -7354,7 +7354,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>2.152243734703611</v>
+        <v>2.121930442665532</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7362,22 +7362,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.08148513381850252</v>
+        <v>0.08150027589968106</v>
       </c>
       <c r="C73">
-        <v>1856.672373236541</v>
+        <v>1724.699202868978</v>
       </c>
       <c r="D73">
-        <v>10454.60637323654</v>
+        <v>10452.78720286898</v>
       </c>
       <c r="E73">
-        <v>-673.0660000000007</v>
+        <v>-542.9120000000003</v>
       </c>
       <c r="F73">
-        <v>9240.933999999999</v>
+        <v>9371.088</v>
       </c>
       <c r="G73">
         <v>643</v>
@@ -7398,28 +7398,28 @@
         <v>1486.333333333333</v>
       </c>
       <c r="M73">
-        <v>700.4627972</v>
+        <v>710.3284704</v>
       </c>
       <c r="N73">
-        <v>785.8705361333333</v>
+        <v>776.0048629333332</v>
       </c>
       <c r="O73">
-        <v>202.7545983224</v>
+        <v>200.2092546368</v>
       </c>
       <c r="P73">
-        <v>583.1159378109332</v>
+        <v>575.7956082965333</v>
       </c>
       <c r="Q73">
-        <v>618.1159378109332</v>
+        <v>610.7956082965333</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1432833717879397</v>
+        <v>0.1464460139274324</v>
       </c>
       <c r="T73">
-        <v>2.251348078243411</v>
+        <v>2.324388312411833</v>
       </c>
       <c r="U73">
         <v>0.07580000000000001</v>
@@ -7436,7 +7436,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>2.121930442665533</v>
+        <v>2.0924591865174</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7444,22 +7444,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.08150027589968106</v>
+        <v>0.08151541798085962</v>
       </c>
       <c r="C74">
-        <v>1724.699202868978</v>
+        <v>1592.726665486525</v>
       </c>
       <c r="D74">
-        <v>10452.78720286898</v>
+        <v>10450.96866548653</v>
       </c>
       <c r="E74">
-        <v>-542.9120000000003</v>
+        <v>-412.7579999999998</v>
       </c>
       <c r="F74">
-        <v>9371.088</v>
+        <v>9501.242</v>
       </c>
       <c r="G74">
         <v>643</v>
@@ -7480,28 +7480,28 @@
         <v>1486.333333333333</v>
       </c>
       <c r="M74">
-        <v>710.3284704</v>
+        <v>720.1941436000001</v>
       </c>
       <c r="N74">
-        <v>776.0048629333332</v>
+        <v>766.1391897333332</v>
       </c>
       <c r="O74">
-        <v>200.2092546368</v>
+        <v>197.6639109512</v>
       </c>
       <c r="P74">
-        <v>575.7956082965333</v>
+        <v>568.4752787821333</v>
       </c>
       <c r="Q74">
-        <v>610.7956082965333</v>
+        <v>603.4752787821333</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1464460139274324</v>
+        <v>0.1498429258550356</v>
       </c>
       <c r="T74">
-        <v>2.324388312411833</v>
+        <v>2.402838934296434</v>
       </c>
       <c r="U74">
         <v>0.07580000000000001</v>
@@ -7518,7 +7518,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>2.0924591865174</v>
+        <v>2.063795362044559</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7526,22 +7526,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.08151541798085962</v>
+        <v>0.08153056006203817</v>
       </c>
       <c r="C75">
-        <v>1592.726665486525</v>
+        <v>1460.754760758868</v>
       </c>
       <c r="D75">
-        <v>10450.96866548653</v>
+        <v>10449.15076075887</v>
       </c>
       <c r="E75">
-        <v>-412.7579999999998</v>
+        <v>-282.6040000000012</v>
       </c>
       <c r="F75">
-        <v>9501.242</v>
+        <v>9631.395999999999</v>
       </c>
       <c r="G75">
         <v>643</v>
@@ -7562,28 +7562,28 @@
         <v>1486.333333333333</v>
       </c>
       <c r="M75">
-        <v>720.1941436000001</v>
+        <v>730.0598168</v>
       </c>
       <c r="N75">
-        <v>766.1391897333332</v>
+        <v>756.2735165333332</v>
       </c>
       <c r="O75">
-        <v>197.6639109512</v>
+        <v>195.1185672656</v>
       </c>
       <c r="P75">
-        <v>568.4752787821333</v>
+        <v>561.1549492677333</v>
       </c>
       <c r="Q75">
-        <v>603.4752787821333</v>
+        <v>596.1549492677333</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1498429258550356</v>
+        <v>0.1535011387001468</v>
       </c>
       <c r="T75">
-        <v>2.402838934296434</v>
+        <v>2.487324219402928</v>
       </c>
       <c r="U75">
         <v>0.07580000000000001</v>
@@ -7600,7 +7600,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>2.063795362044559</v>
+        <v>2.035906235530443</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7608,22 +7608,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.08153056006203817</v>
+        <v>0.08154570214321671</v>
       </c>
       <c r="C76">
-        <v>1460.754760758868</v>
+        <v>1328.783488355912</v>
       </c>
       <c r="D76">
-        <v>10449.15076075887</v>
+        <v>10447.33348835591</v>
       </c>
       <c r="E76">
-        <v>-282.6040000000012</v>
+        <v>-152.4500000000007</v>
       </c>
       <c r="F76">
-        <v>9631.395999999999</v>
+        <v>9761.549999999999</v>
       </c>
       <c r="G76">
         <v>643</v>
@@ -7644,28 +7644,28 @@
         <v>1486.333333333333</v>
       </c>
       <c r="M76">
-        <v>730.0598168</v>
+        <v>739.92549</v>
       </c>
       <c r="N76">
-        <v>756.2735165333332</v>
+        <v>746.4078433333333</v>
       </c>
       <c r="O76">
-        <v>195.1185672656</v>
+        <v>192.57322358</v>
       </c>
       <c r="P76">
-        <v>561.1549492677333</v>
+        <v>553.8346197533333</v>
       </c>
       <c r="Q76">
-        <v>596.1549492677333</v>
+        <v>588.8346197533333</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1535011387001468</v>
+        <v>0.1574520085728669</v>
       </c>
       <c r="T76">
-        <v>2.487324219402928</v>
+        <v>2.578568327317941</v>
       </c>
       <c r="U76">
         <v>0.07580000000000001</v>
@@ -7682,7 +7682,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>2.035906235530443</v>
+        <v>2.008760819056704</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7690,22 +7690,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.08154570214321671</v>
+        <v>0.08956850822439526</v>
       </c>
       <c r="C77">
-        <v>1328.783488355912</v>
+        <v>317.1661714055263</v>
       </c>
       <c r="D77">
-        <v>10447.33348835591</v>
+        <v>9565.870171405526</v>
       </c>
       <c r="E77">
-        <v>-152.4500000000007</v>
+        <v>-22.29600000000028</v>
       </c>
       <c r="F77">
-        <v>9761.549999999999</v>
+        <v>9891.704</v>
       </c>
       <c r="G77">
         <v>643</v>
@@ -7726,45 +7726,45 @@
         <v>1486.333333333333</v>
       </c>
       <c r="M77">
-        <v>739.92549</v>
+        <v>890.2533599999999</v>
       </c>
       <c r="N77">
-        <v>746.4078433333333</v>
+        <v>596.0799733333333</v>
       </c>
       <c r="O77">
-        <v>192.57322358</v>
+        <v>153.78863312</v>
       </c>
       <c r="P77">
-        <v>553.8346197533333</v>
+        <v>442.2913402133333</v>
       </c>
       <c r="Q77">
-        <v>588.8346197533333</v>
+        <v>477.2913402133333</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1574520085728669</v>
+        <v>0.1617321176016469</v>
       </c>
       <c r="T77">
-        <v>2.578568327317941</v>
+        <v>2.677416110892539</v>
       </c>
       <c r="U77">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V77">
         <v>0.258</v>
       </c>
       <c r="W77">
-        <v>0.0562436</v>
+        <v>0.06677999999999999</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y77">
-        <v>2.008760819056704</v>
+        <v>1.669562171979147</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7772,22 +7772,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.08956850822439526</v>
+        <v>0.08968901430557381</v>
       </c>
       <c r="C78">
-        <v>317.1661714055263</v>
+        <v>174.90463173432</v>
       </c>
       <c r="D78">
-        <v>9565.870171405526</v>
+        <v>9553.76263173432</v>
       </c>
       <c r="E78">
-        <v>-22.29600000000028</v>
+        <v>107.8580000000002</v>
       </c>
       <c r="F78">
-        <v>9891.704</v>
+        <v>10021.858</v>
       </c>
       <c r="G78">
         <v>643</v>
@@ -7808,28 +7808,28 @@
         <v>1486.333333333333</v>
       </c>
       <c r="M78">
-        <v>890.2533599999999</v>
+        <v>901.96722</v>
       </c>
       <c r="N78">
-        <v>596.0799733333333</v>
+        <v>584.3661133333333</v>
       </c>
       <c r="O78">
-        <v>153.78863312</v>
+        <v>150.76645724</v>
       </c>
       <c r="P78">
-        <v>442.2913402133333</v>
+        <v>433.5996560933332</v>
       </c>
       <c r="Q78">
-        <v>477.2913402133333</v>
+        <v>468.5996560933332</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1617321176016469</v>
+        <v>0.166384410024234</v>
       </c>
       <c r="T78">
-        <v>2.677416110892539</v>
+        <v>2.784859353908406</v>
       </c>
       <c r="U78">
         <v>0.09</v>
@@ -7846,7 +7846,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>1.669562171979147</v>
+        <v>1.647879546369028</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7854,22 +7854,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.08968901430557381</v>
+        <v>0.08980952038675236</v>
       </c>
       <c r="C79">
-        <v>174.90463173432</v>
+        <v>32.67370239053889</v>
       </c>
       <c r="D79">
-        <v>9553.76263173432</v>
+        <v>9541.68570239054</v>
       </c>
       <c r="E79">
-        <v>107.8580000000002</v>
+        <v>238.0120000000006</v>
       </c>
       <c r="F79">
-        <v>10021.858</v>
+        <v>10152.012</v>
       </c>
       <c r="G79">
         <v>643</v>
@@ -7890,28 +7890,28 @@
         <v>1486.333333333333</v>
       </c>
       <c r="M79">
-        <v>901.96722</v>
+        <v>913.6810800000001</v>
       </c>
       <c r="N79">
-        <v>584.3661133333333</v>
+        <v>572.6522533333332</v>
       </c>
       <c r="O79">
-        <v>150.76645724</v>
+        <v>147.74428136</v>
       </c>
       <c r="P79">
-        <v>433.5996560933332</v>
+        <v>424.9079719733332</v>
       </c>
       <c r="Q79">
-        <v>468.5996560933332</v>
+        <v>459.9079719733332</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.166384410024234</v>
+        <v>0.1714596381216017</v>
       </c>
       <c r="T79">
-        <v>2.784859353908406</v>
+        <v>2.902070164471171</v>
       </c>
       <c r="U79">
         <v>0.09</v>
@@ -7928,7 +7928,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>1.647879546369028</v>
+        <v>1.626752885518143</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7936,22 +7936,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.08980952038675236</v>
+        <v>0.08993002646793091</v>
       </c>
       <c r="C80">
-        <v>32.67370239053889</v>
+        <v>-109.5267325629829</v>
       </c>
       <c r="D80">
-        <v>9541.68570239054</v>
+        <v>9529.639267437018</v>
       </c>
       <c r="E80">
-        <v>238.0120000000006</v>
+        <v>368.1660000000011</v>
       </c>
       <c r="F80">
-        <v>10152.012</v>
+        <v>10282.166</v>
       </c>
       <c r="G80">
         <v>643</v>
@@ -7972,28 +7972,28 @@
         <v>1486.333333333333</v>
       </c>
       <c r="M80">
-        <v>913.6810800000001</v>
+        <v>925.39494</v>
       </c>
       <c r="N80">
-        <v>572.6522533333332</v>
+        <v>560.9383933333332</v>
       </c>
       <c r="O80">
-        <v>147.74428136</v>
+        <v>144.72210548</v>
       </c>
       <c r="P80">
-        <v>424.9079719733332</v>
+        <v>416.2162878533333</v>
       </c>
       <c r="Q80">
-        <v>459.9079719733332</v>
+        <v>451.2162878533333</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1714596381216017</v>
+        <v>0.1770182212758615</v>
       </c>
       <c r="T80">
-        <v>2.902070164471171</v>
+        <v>3.030443909373246</v>
       </c>
       <c r="U80">
         <v>0.09</v>
@@ -8010,7 +8010,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>1.626752885518143</v>
+        <v>1.606161076840698</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -8018,22 +8018,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.08993002646793091</v>
+        <v>0.09005053254910947</v>
       </c>
       <c r="C81">
-        <v>-109.5267325629829</v>
+        <v>-251.6967884786554</v>
       </c>
       <c r="D81">
-        <v>9529.639267437018</v>
+        <v>9517.623211521344</v>
       </c>
       <c r="E81">
-        <v>368.1660000000011</v>
+        <v>498.3199999999997</v>
       </c>
       <c r="F81">
-        <v>10282.166</v>
+        <v>10412.32</v>
       </c>
       <c r="G81">
         <v>643</v>
@@ -8054,28 +8054,28 @@
         <v>1486.333333333333</v>
       </c>
       <c r="M81">
-        <v>925.39494</v>
+        <v>937.1088</v>
       </c>
       <c r="N81">
-        <v>560.9383933333332</v>
+        <v>549.2245333333333</v>
       </c>
       <c r="O81">
-        <v>144.72210548</v>
+        <v>141.6999296</v>
       </c>
       <c r="P81">
-        <v>416.2162878533333</v>
+        <v>407.5246037333333</v>
       </c>
       <c r="Q81">
-        <v>451.2162878533333</v>
+        <v>442.5246037333333</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.1770182212758615</v>
+        <v>0.1831326627455473</v>
       </c>
       <c r="T81">
-        <v>3.030443909373246</v>
+        <v>3.171655028765528</v>
       </c>
       <c r="U81">
         <v>0.09</v>
@@ -8092,7 +8092,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>1.606161076840698</v>
+        <v>1.58608406338019</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8100,22 +8100,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.09005053254910947</v>
+        <v>0.09017103863028801</v>
       </c>
       <c r="C82">
-        <v>-251.6967884786554</v>
+        <v>-393.8365801278305</v>
       </c>
       <c r="D82">
-        <v>9517.623211521344</v>
+        <v>9505.63741987217</v>
       </c>
       <c r="E82">
-        <v>498.3199999999997</v>
+        <v>628.4740000000002</v>
       </c>
       <c r="F82">
-        <v>10412.32</v>
+        <v>10542.474</v>
       </c>
       <c r="G82">
         <v>643</v>
@@ -8136,28 +8136,28 @@
         <v>1486.333333333333</v>
       </c>
       <c r="M82">
-        <v>937.1088</v>
+        <v>948.8226599999999</v>
       </c>
       <c r="N82">
-        <v>549.2245333333333</v>
+        <v>537.5106733333333</v>
       </c>
       <c r="O82">
-        <v>141.6999296</v>
+        <v>138.67775372</v>
       </c>
       <c r="P82">
-        <v>407.5246037333333</v>
+        <v>398.8329196133333</v>
       </c>
       <c r="Q82">
-        <v>442.5246037333333</v>
+        <v>433.8329196133333</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.1831326627455473</v>
+        <v>0.1898907296330949</v>
       </c>
       <c r="T82">
-        <v>3.171655028765528</v>
+        <v>3.327730476514893</v>
       </c>
       <c r="U82">
         <v>0.09</v>
@@ -8174,7 +8174,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>1.58608406338019</v>
+        <v>1.566502778647101</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8182,22 +8182,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.09017103863028801</v>
+        <v>0.09029154471146655</v>
       </c>
       <c r="C83">
-        <v>-393.8365801278305</v>
+        <v>-535.9462217044456</v>
       </c>
       <c r="D83">
-        <v>9505.63741987217</v>
+        <v>9493.681778295555</v>
       </c>
       <c r="E83">
-        <v>628.4740000000002</v>
+        <v>758.6280000000006</v>
       </c>
       <c r="F83">
-        <v>10542.474</v>
+        <v>10672.628</v>
       </c>
       <c r="G83">
         <v>643</v>
@@ -8218,28 +8218,28 @@
         <v>1486.333333333333</v>
       </c>
       <c r="M83">
-        <v>948.8226599999999</v>
+        <v>960.53652</v>
       </c>
       <c r="N83">
-        <v>537.5106733333333</v>
+        <v>525.7968133333333</v>
       </c>
       <c r="O83">
-        <v>138.67775372</v>
+        <v>135.65557784</v>
       </c>
       <c r="P83">
-        <v>398.8329196133333</v>
+        <v>390.1412354933333</v>
       </c>
       <c r="Q83">
-        <v>433.8329196133333</v>
+        <v>425.1412354933333</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.1898907296330949</v>
+        <v>0.197399692841481</v>
       </c>
       <c r="T83">
-        <v>3.327730476514893</v>
+        <v>3.501147640680854</v>
       </c>
       <c r="U83">
         <v>0.09</v>
@@ -8256,7 +8256,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>1.566502778647101</v>
+        <v>1.547399086224575</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8264,22 +8264,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.09029154471146655</v>
+        <v>0.09041205079264511</v>
       </c>
       <c r="C84">
-        <v>-535.9462217044456</v>
+        <v>-678.0258268286561</v>
       </c>
       <c r="D84">
-        <v>9493.681778295555</v>
+        <v>9481.756173171345</v>
       </c>
       <c r="E84">
-        <v>758.6280000000006</v>
+        <v>888.7820000000011</v>
       </c>
       <c r="F84">
-        <v>10672.628</v>
+        <v>10802.782</v>
       </c>
       <c r="G84">
         <v>643</v>
@@ -8300,28 +8300,28 @@
         <v>1486.333333333333</v>
       </c>
       <c r="M84">
-        <v>960.53652</v>
+        <v>972.2503800000001</v>
       </c>
       <c r="N84">
-        <v>525.7968133333333</v>
+        <v>514.0829533333332</v>
       </c>
       <c r="O84">
-        <v>135.65557784</v>
+        <v>132.63340196</v>
       </c>
       <c r="P84">
-        <v>390.1412354933333</v>
+        <v>381.4495513733332</v>
       </c>
       <c r="Q84">
-        <v>425.1412354933333</v>
+        <v>416.4495513733332</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.197399692841481</v>
+        <v>0.2057920634861478</v>
       </c>
       <c r="T84">
-        <v>3.501147640680854</v>
+        <v>3.694966824160458</v>
       </c>
       <c r="U84">
         <v>0.09</v>
@@ -8338,7 +8338,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>1.547399086224575</v>
+        <v>1.528755723739942</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8346,22 +8346,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.09041205079264511</v>
+        <v>0.09053255687382367</v>
       </c>
       <c r="C85">
-        <v>-678.0258268286561</v>
+        <v>-820.0755085504279</v>
       </c>
       <c r="D85">
-        <v>9481.756173171345</v>
+        <v>9469.860491449574</v>
       </c>
       <c r="E85">
-        <v>888.7820000000011</v>
+        <v>1018.936000000002</v>
       </c>
       <c r="F85">
-        <v>10802.782</v>
+        <v>10932.936</v>
       </c>
       <c r="G85">
         <v>643</v>
@@ -8382,28 +8382,28 @@
         <v>1486.333333333333</v>
       </c>
       <c r="M85">
-        <v>972.2503800000001</v>
+        <v>983.9642400000001</v>
       </c>
       <c r="N85">
-        <v>514.0829533333332</v>
+        <v>502.3690933333331</v>
       </c>
       <c r="O85">
-        <v>132.63340196</v>
+        <v>129.6112260799999</v>
       </c>
       <c r="P85">
-        <v>381.4495513733332</v>
+        <v>372.7578672533332</v>
       </c>
       <c r="Q85">
-        <v>416.4495513733332</v>
+        <v>407.7578672533332</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2057920634861478</v>
+        <v>0.215233480461398</v>
       </c>
       <c r="T85">
-        <v>3.694966824160458</v>
+        <v>3.913013405575012</v>
       </c>
       <c r="U85">
         <v>0.09</v>
@@ -8420,7 +8420,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>1.528755723739942</v>
+        <v>1.510556250838275</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8428,22 +8428,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.09053255687382367</v>
+        <v>0.1298506326657083</v>
       </c>
       <c r="C86">
-        <v>-820.0755085504261</v>
+        <v>-3700.730123468952</v>
       </c>
       <c r="D86">
-        <v>9469.860491449574</v>
+        <v>6719.359876531048</v>
       </c>
       <c r="E86">
-        <v>1018.936</v>
+        <v>1149.09</v>
       </c>
       <c r="F86">
-        <v>10932.936</v>
+        <v>11063.09</v>
       </c>
       <c r="G86">
         <v>643</v>
@@ -8464,45 +8464,45 @@
         <v>1486.333333333333</v>
       </c>
       <c r="M86">
-        <v>983.9642399999999</v>
+        <v>1624.061612</v>
       </c>
       <c r="N86">
-        <v>502.3690933333334</v>
+        <v>-137.7282786666669</v>
       </c>
       <c r="O86">
-        <v>129.61122608</v>
+        <v>-35.53389589600007</v>
       </c>
       <c r="P86">
-        <v>372.7578672533333</v>
+        <v>-102.1943827706669</v>
       </c>
       <c r="Q86">
-        <v>407.7578672533333</v>
+        <v>-67.19438277066686</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2152334804613979</v>
+        <v>0.2302248681803915</v>
       </c>
       <c r="T86">
-        <v>3.913013405575009</v>
+        <v>4.259234830955924</v>
       </c>
       <c r="U86">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V86">
-        <v>0.258</v>
+        <v>0.2361203523108703</v>
       </c>
       <c r="W86">
-        <v>0.06677999999999999</v>
+        <v>0.1121375322807642</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y86">
-        <v>1.510556250838276</v>
+        <v>0.9151951639956213</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8510,22 +8510,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1298506326657083</v>
+        <v>0.1308606326657084</v>
       </c>
       <c r="C87">
-        <v>-3700.730123468952</v>
+        <v>-3880.646021892071</v>
       </c>
       <c r="D87">
-        <v>6719.359876531048</v>
+        <v>6669.597978107928</v>
       </c>
       <c r="E87">
-        <v>1149.09</v>
+        <v>1279.243999999999</v>
       </c>
       <c r="F87">
-        <v>11063.09</v>
+        <v>11193.244</v>
       </c>
       <c r="G87">
         <v>643</v>
@@ -8546,37 +8546,37 @@
         <v>1486.333333333333</v>
       </c>
       <c r="M87">
-        <v>1624.061612</v>
+        <v>1643.1682192</v>
       </c>
       <c r="N87">
-        <v>-137.7282786666669</v>
+        <v>-156.8348858666668</v>
       </c>
       <c r="O87">
-        <v>-35.53389589600007</v>
+        <v>-40.46340055360004</v>
       </c>
       <c r="P87">
-        <v>-102.1943827706669</v>
+        <v>-116.3714853130668</v>
       </c>
       <c r="Q87">
-        <v>-67.19438277066686</v>
+        <v>-81.37148531306677</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2302248681803915</v>
+        <v>0.2433980730504195</v>
       </c>
       <c r="T87">
-        <v>4.259234830955924</v>
+        <v>4.563465890309919</v>
       </c>
       <c r="U87">
         <v>0.1468</v>
       </c>
       <c r="V87">
-        <v>0.2361203523108703</v>
+        <v>0.2333747668188834</v>
       </c>
       <c r="W87">
-        <v>0.1121375322807642</v>
+        <v>0.1125405842309879</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8584,7 +8584,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.9151951639956213</v>
+        <v>0.9045533597631141</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8592,22 +8592,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1308606326657084</v>
+        <v>0.1318706326657083</v>
       </c>
       <c r="C88">
-        <v>-3880.646021892071</v>
+        <v>-4059.830290240569</v>
       </c>
       <c r="D88">
-        <v>6669.597978107928</v>
+        <v>6620.56770975943</v>
       </c>
       <c r="E88">
-        <v>1279.243999999999</v>
+        <v>1409.397999999999</v>
       </c>
       <c r="F88">
-        <v>11193.244</v>
+        <v>11323.398</v>
       </c>
       <c r="G88">
         <v>643</v>
@@ -8628,37 +8628,37 @@
         <v>1486.333333333333</v>
       </c>
       <c r="M88">
-        <v>1643.1682192</v>
+        <v>1662.2748264</v>
       </c>
       <c r="N88">
-        <v>-156.8348858666668</v>
+        <v>-175.9414930666667</v>
       </c>
       <c r="O88">
-        <v>-40.46340055360004</v>
+        <v>-45.3929052112</v>
       </c>
       <c r="P88">
-        <v>-116.3714853130668</v>
+        <v>-130.5485878554667</v>
       </c>
       <c r="Q88">
-        <v>-81.37148531306677</v>
+        <v>-95.54858785546668</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2433980730504195</v>
+        <v>0.2585979248235287</v>
       </c>
       <c r="T88">
-        <v>4.563465890309919</v>
+        <v>4.914501728026067</v>
       </c>
       <c r="U88">
         <v>0.1468</v>
       </c>
       <c r="V88">
-        <v>0.2333747668188834</v>
+        <v>0.2306922982347584</v>
       </c>
       <c r="W88">
-        <v>0.1125405842309879</v>
+        <v>0.1129343706191375</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8666,7 +8666,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.9045533597631141</v>
+        <v>0.8941561947083658</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8674,22 +8674,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1318706326657083</v>
+        <v>0.1328806326657083</v>
       </c>
       <c r="C89">
-        <v>-4059.830290240569</v>
+        <v>-4238.298946078256</v>
       </c>
       <c r="D89">
-        <v>6620.56770975943</v>
+        <v>6572.253053921744</v>
       </c>
       <c r="E89">
-        <v>1409.397999999999</v>
+        <v>1539.552</v>
       </c>
       <c r="F89">
-        <v>11323.398</v>
+        <v>11453.552</v>
       </c>
       <c r="G89">
         <v>643</v>
@@ -8710,37 +8710,37 @@
         <v>1486.333333333333</v>
       </c>
       <c r="M89">
-        <v>1662.2748264</v>
+        <v>1681.3814336</v>
       </c>
       <c r="N89">
-        <v>-175.9414930666667</v>
+        <v>-195.0481002666668</v>
       </c>
       <c r="O89">
-        <v>-45.3929052112</v>
+        <v>-50.32240986880003</v>
       </c>
       <c r="P89">
-        <v>-130.5485878554667</v>
+        <v>-144.7256903978667</v>
       </c>
       <c r="Q89">
-        <v>-95.54858785546668</v>
+        <v>-109.7256903978667</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.2585979248235287</v>
+        <v>0.2763310852254894</v>
       </c>
       <c r="T89">
-        <v>4.914501728026067</v>
+        <v>5.324043538694907</v>
       </c>
       <c r="U89">
         <v>0.1468</v>
       </c>
       <c r="V89">
-        <v>0.2306922982347584</v>
+        <v>0.228070794845727</v>
       </c>
       <c r="W89">
-        <v>0.1129343706191375</v>
+        <v>0.1133192073166473</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8748,7 +8748,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.8941561947083658</v>
+        <v>0.883995328859407</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8756,22 +8756,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1328806326657083</v>
+        <v>0.1338906326657083</v>
       </c>
       <c r="C90">
-        <v>-4238.298946078256</v>
+        <v>-4416.067542793368</v>
       </c>
       <c r="D90">
-        <v>6572.253053921744</v>
+        <v>6524.638457206632</v>
       </c>
       <c r="E90">
-        <v>1539.552</v>
+        <v>1669.706</v>
       </c>
       <c r="F90">
-        <v>11453.552</v>
+        <v>11583.706</v>
       </c>
       <c r="G90">
         <v>643</v>
@@ -8792,37 +8792,37 @@
         <v>1486.333333333333</v>
       </c>
       <c r="M90">
-        <v>1681.3814336</v>
+        <v>1700.4880408</v>
       </c>
       <c r="N90">
-        <v>-195.0481002666668</v>
+        <v>-214.1547074666669</v>
       </c>
       <c r="O90">
-        <v>-50.32240986880003</v>
+        <v>-55.25191452640006</v>
       </c>
       <c r="P90">
-        <v>-144.7256903978667</v>
+        <v>-158.9027929402668</v>
       </c>
       <c r="Q90">
-        <v>-109.7256903978667</v>
+        <v>-123.9027929402668</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.2763310852254894</v>
+        <v>0.2972884566096249</v>
       </c>
       <c r="T90">
-        <v>5.324043538694907</v>
+        <v>5.80804749675808</v>
       </c>
       <c r="U90">
         <v>0.1468</v>
       </c>
       <c r="V90">
-        <v>0.228070794845727</v>
+        <v>0.2255082016452132</v>
       </c>
       <c r="W90">
-        <v>0.1133192073166473</v>
+        <v>0.1136953959984827</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8830,7 +8830,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.883995328859407</v>
+        <v>0.8740627970744699</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8838,22 +8838,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1338906326657083</v>
+        <v>0.1349006326657084</v>
       </c>
       <c r="C91">
-        <v>-4416.067542793368</v>
+        <v>-4593.151186291892</v>
       </c>
       <c r="D91">
-        <v>6524.638457206632</v>
+        <v>6477.708813708108</v>
       </c>
       <c r="E91">
-        <v>1669.706</v>
+        <v>1799.860000000001</v>
       </c>
       <c r="F91">
-        <v>11583.706</v>
+        <v>11713.86</v>
       </c>
       <c r="G91">
         <v>643</v>
@@ -8874,37 +8874,37 @@
         <v>1486.333333333333</v>
       </c>
       <c r="M91">
-        <v>1700.4880408</v>
+        <v>1719.594648</v>
       </c>
       <c r="N91">
-        <v>-214.1547074666669</v>
+        <v>-233.261314666667</v>
       </c>
       <c r="O91">
-        <v>-55.25191452640006</v>
+        <v>-60.18141918400008</v>
       </c>
       <c r="P91">
-        <v>-158.9027929402668</v>
+        <v>-173.0798954826669</v>
       </c>
       <c r="Q91">
-        <v>-123.9027929402668</v>
+        <v>-138.0798954826669</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.2972884566096249</v>
+        <v>0.3224373022705874</v>
       </c>
       <c r="T91">
-        <v>5.80804749675808</v>
+        <v>6.388852246433889</v>
       </c>
       <c r="U91">
         <v>0.1468</v>
       </c>
       <c r="V91">
-        <v>0.2255082016452132</v>
+        <v>0.2230025549602664</v>
       </c>
       <c r="W91">
-        <v>0.1136953959984827</v>
+        <v>0.1140632249318329</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8912,7 +8912,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.8740627970744699</v>
+        <v>0.8643509882180868</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8920,22 +8920,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1349006326657084</v>
+        <v>0.1359106326657084</v>
       </c>
       <c r="C92">
-        <v>-4593.151186291892</v>
+        <v>-4769.564550975632</v>
       </c>
       <c r="D92">
-        <v>6477.708813708108</v>
+        <v>6431.449449024367</v>
       </c>
       <c r="E92">
-        <v>1799.860000000001</v>
+        <v>1930.013999999999</v>
       </c>
       <c r="F92">
-        <v>11713.86</v>
+        <v>11844.014</v>
       </c>
       <c r="G92">
         <v>643</v>
@@ -8956,37 +8956,37 @@
         <v>1486.333333333333</v>
       </c>
       <c r="M92">
-        <v>1719.594648</v>
+        <v>1738.7012552</v>
       </c>
       <c r="N92">
-        <v>-233.261314666667</v>
+        <v>-252.3679218666668</v>
       </c>
       <c r="O92">
-        <v>-60.18141918400008</v>
+        <v>-65.11092384160006</v>
       </c>
       <c r="P92">
-        <v>-173.0798954826669</v>
+        <v>-187.2569980250668</v>
       </c>
       <c r="Q92">
-        <v>-138.0798954826669</v>
+        <v>-152.2569980250668</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.3224373022705874</v>
+        <v>0.3531747803006527</v>
       </c>
       <c r="T92">
-        <v>6.388852246433889</v>
+        <v>7.098724718259877</v>
       </c>
       <c r="U92">
         <v>0.1468</v>
       </c>
       <c r="V92">
-        <v>0.2230025549602664</v>
+        <v>0.2205519774332305</v>
       </c>
       <c r="W92">
-        <v>0.1140632249318329</v>
+        <v>0.1144229697128018</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8994,7 +8994,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.8643509882180868</v>
+        <v>0.8548526257101958</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -9002,22 +9002,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1359106326657084</v>
+        <v>0.1369206326657084</v>
       </c>
       <c r="C93">
-        <v>-4769.564550975632</v>
+        <v>-4945.321895040503</v>
       </c>
       <c r="D93">
-        <v>6431.449449024367</v>
+        <v>6385.846104959497</v>
       </c>
       <c r="E93">
-        <v>1930.013999999999</v>
+        <v>2060.168</v>
       </c>
       <c r="F93">
-        <v>11844.014</v>
+        <v>11974.168</v>
       </c>
       <c r="G93">
         <v>643</v>
@@ -9038,37 +9038,37 @@
         <v>1486.333333333333</v>
       </c>
       <c r="M93">
-        <v>1738.7012552</v>
+        <v>1757.8078624</v>
       </c>
       <c r="N93">
-        <v>-252.3679218666668</v>
+        <v>-271.4745290666669</v>
       </c>
       <c r="O93">
-        <v>-65.11092384160006</v>
+        <v>-70.04042849920008</v>
       </c>
       <c r="P93">
-        <v>-187.2569980250668</v>
+        <v>-201.4341005674669</v>
       </c>
       <c r="Q93">
-        <v>-152.2569980250668</v>
+        <v>-166.4341005674669</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.3531747803006527</v>
+        <v>0.3915966278382343</v>
       </c>
       <c r="T93">
-        <v>7.098724718259877</v>
+        <v>7.986065308042363</v>
       </c>
       <c r="U93">
         <v>0.1468</v>
       </c>
       <c r="V93">
-        <v>0.2205519774332305</v>
+        <v>0.2181546733306954</v>
       </c>
       <c r="W93">
-        <v>0.1144229697128018</v>
+        <v>0.1147748939550539</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -9076,7 +9076,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.8548526257101958</v>
+        <v>0.8455607493437806</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9084,22 +9084,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1369206326657084</v>
+        <v>0.1379306326657083</v>
       </c>
       <c r="C94">
-        <v>-4945.321895040503</v>
+        <v>-5120.437075128534</v>
       </c>
       <c r="D94">
-        <v>6385.846104959497</v>
+        <v>6340.884924871466</v>
       </c>
       <c r="E94">
-        <v>2060.168</v>
+        <v>2190.322</v>
       </c>
       <c r="F94">
-        <v>11974.168</v>
+        <v>12104.322</v>
       </c>
       <c r="G94">
         <v>643</v>
@@ -9120,37 +9120,37 @@
         <v>1486.333333333333</v>
       </c>
       <c r="M94">
-        <v>1757.8078624</v>
+        <v>1776.9144696</v>
       </c>
       <c r="N94">
-        <v>-271.4745290666669</v>
+        <v>-290.5811362666668</v>
       </c>
       <c r="O94">
-        <v>-70.04042849920008</v>
+        <v>-74.96993315680004</v>
       </c>
       <c r="P94">
-        <v>-201.4341005674669</v>
+        <v>-215.6112031098668</v>
       </c>
       <c r="Q94">
-        <v>-166.4341005674669</v>
+        <v>-180.6112031098668</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.3915966278382343</v>
+        <v>0.4409961461008393</v>
       </c>
       <c r="T94">
-        <v>7.986065308042363</v>
+        <v>9.126931780619845</v>
       </c>
       <c r="U94">
         <v>0.1468</v>
       </c>
       <c r="V94">
-        <v>0.2181546733306954</v>
+        <v>0.2158089241550965</v>
       </c>
       <c r="W94">
-        <v>0.1147748939550539</v>
+        <v>0.1151192499340318</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9158,7 +9158,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.8455607493437806</v>
+        <v>0.8364686982755679</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9166,22 +9166,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.1379306326657083</v>
+        <v>0.1389406326657084</v>
       </c>
       <c r="C95">
-        <v>-5120.437075128534</v>
+        <v>-5294.923560365267</v>
       </c>
       <c r="D95">
-        <v>6340.884924871466</v>
+        <v>6296.552439634734</v>
       </c>
       <c r="E95">
-        <v>2190.322</v>
+        <v>2320.476000000001</v>
       </c>
       <c r="F95">
-        <v>12104.322</v>
+        <v>12234.476</v>
       </c>
       <c r="G95">
         <v>643</v>
@@ -9202,37 +9202,37 @@
         <v>1486.333333333333</v>
       </c>
       <c r="M95">
-        <v>1776.9144696</v>
+        <v>1796.0210768</v>
       </c>
       <c r="N95">
-        <v>-290.5811362666668</v>
+        <v>-309.6877434666669</v>
       </c>
       <c r="O95">
-        <v>-74.96993315680004</v>
+        <v>-79.89943781440007</v>
       </c>
       <c r="P95">
-        <v>-215.6112031098668</v>
+        <v>-229.7883056522668</v>
       </c>
       <c r="Q95">
-        <v>-180.6112031098668</v>
+        <v>-194.7883056522668</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.4409961461008393</v>
+        <v>0.5068621704509793</v>
       </c>
       <c r="T95">
-        <v>9.126931780619845</v>
+        <v>10.64808707738982</v>
       </c>
       <c r="U95">
         <v>0.1468</v>
       </c>
       <c r="V95">
-        <v>0.2158089241550965</v>
+        <v>0.2135130845364253</v>
       </c>
       <c r="W95">
-        <v>0.1151192499340318</v>
+        <v>0.1154562791900528</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9240,7 +9240,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.8364686982755679</v>
+        <v>0.8275700951024235</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9248,22 +9248,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1389406326657084</v>
+        <v>0.1399506326657083</v>
       </c>
       <c r="C96">
-        <v>-5294.923560365267</v>
+        <v>-5468.794445812349</v>
       </c>
       <c r="D96">
-        <v>6296.552439634734</v>
+        <v>6252.835554187652</v>
       </c>
       <c r="E96">
-        <v>2320.476000000001</v>
+        <v>2450.630000000001</v>
       </c>
       <c r="F96">
-        <v>12234.476</v>
+        <v>12364.63</v>
       </c>
       <c r="G96">
         <v>643</v>
@@ -9284,37 +9284,37 @@
         <v>1486.333333333333</v>
       </c>
       <c r="M96">
-        <v>1796.0210768</v>
+        <v>1815.127684</v>
       </c>
       <c r="N96">
-        <v>-309.6877434666669</v>
+        <v>-328.794350666667</v>
       </c>
       <c r="O96">
-        <v>-79.89943781440007</v>
+        <v>-84.82894247200009</v>
       </c>
       <c r="P96">
-        <v>-229.7883056522668</v>
+        <v>-243.9654081946669</v>
       </c>
       <c r="Q96">
-        <v>-194.7883056522668</v>
+        <v>-208.9654081946669</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.5068621704509793</v>
+        <v>0.5990746045411753</v>
       </c>
       <c r="T96">
-        <v>10.64808707738982</v>
+        <v>12.77770449286779</v>
       </c>
       <c r="U96">
         <v>0.1468</v>
       </c>
       <c r="V96">
-        <v>0.2135130845364253</v>
+        <v>0.2112655783834103</v>
       </c>
       <c r="W96">
-        <v>0.1154562791900528</v>
+        <v>0.1157862130933154</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9322,7 +9322,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.8275700951024235</v>
+        <v>0.8188588309434506</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9330,22 +9330,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1399506326657083</v>
+        <v>0.1409606326657084</v>
       </c>
       <c r="C97">
-        <v>-5468.794445812349</v>
+        <v>-5642.062465363614</v>
       </c>
       <c r="D97">
-        <v>6252.835554187652</v>
+        <v>6209.721534636387</v>
       </c>
       <c r="E97">
-        <v>2450.630000000001</v>
+        <v>2580.784000000001</v>
       </c>
       <c r="F97">
-        <v>12364.63</v>
+        <v>12494.784</v>
       </c>
       <c r="G97">
         <v>643</v>
@@ -9366,37 +9366,37 @@
         <v>1486.333333333333</v>
       </c>
       <c r="M97">
-        <v>1815.127684</v>
+        <v>1834.2342912</v>
       </c>
       <c r="N97">
-        <v>-328.794350666667</v>
+        <v>-347.9009578666671</v>
       </c>
       <c r="O97">
-        <v>-84.82894247200009</v>
+        <v>-89.75844712960011</v>
       </c>
       <c r="P97">
-        <v>-243.9654081946669</v>
+        <v>-258.142510737067</v>
       </c>
       <c r="Q97">
-        <v>-208.9654081946669</v>
+        <v>-223.142510737067</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.5990746045411753</v>
+        <v>0.7373932556764695</v>
       </c>
       <c r="T97">
-        <v>12.77770449286779</v>
+        <v>15.97213061608475</v>
       </c>
       <c r="U97">
         <v>0.1468</v>
       </c>
       <c r="V97">
-        <v>0.2112655783834103</v>
+        <v>0.2090648952752497</v>
       </c>
       <c r="W97">
-        <v>0.1157862130933154</v>
+        <v>0.1161092733735933</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9404,7 +9404,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.8188588309434506</v>
+        <v>0.8103290514544563</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9412,22 +9412,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.1409606326657084</v>
+        <v>0.1419706326657083</v>
       </c>
       <c r="C98">
-        <v>-5642.062465363612</v>
+        <v>-5814.740004111277</v>
       </c>
       <c r="D98">
-        <v>6209.721534636387</v>
+        <v>6167.197995888723</v>
       </c>
       <c r="E98">
-        <v>2580.784</v>
+        <v>2710.938</v>
       </c>
       <c r="F98">
-        <v>12494.784</v>
+        <v>12624.938</v>
       </c>
       <c r="G98">
         <v>643</v>
@@ -9448,37 +9448,37 @@
         <v>1486.333333333333</v>
       </c>
       <c r="M98">
-        <v>1834.2342912</v>
+        <v>1853.3408984</v>
       </c>
       <c r="N98">
-        <v>-347.9009578666669</v>
+        <v>-367.007565066667</v>
       </c>
       <c r="O98">
-        <v>-89.75844712960006</v>
+        <v>-94.68795178720008</v>
       </c>
       <c r="P98">
-        <v>-258.1425107370668</v>
+        <v>-272.3196132794669</v>
       </c>
       <c r="Q98">
-        <v>-223.1425107370668</v>
+        <v>-237.3196132794669</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.7373932556764677</v>
+        <v>0.9679243409019569</v>
       </c>
       <c r="T98">
-        <v>15.97213061608471</v>
+        <v>21.29617415477961</v>
       </c>
       <c r="U98">
         <v>0.1468</v>
       </c>
       <c r="V98">
-        <v>0.2090648952752498</v>
+        <v>0.2069095870765358</v>
       </c>
       <c r="W98">
-        <v>0.1161092733735933</v>
+        <v>0.1164256726171645</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9486,7 +9486,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.8103290514544563</v>
+        <v>0.8019751437075032</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9494,22 +9494,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.1419706326657083</v>
+        <v>0.1977686658066416</v>
       </c>
       <c r="C99">
-        <v>-5814.740004111277</v>
+        <v>-7637.648055004642</v>
       </c>
       <c r="D99">
-        <v>6167.197995888723</v>
+        <v>4474.443944995357</v>
       </c>
       <c r="E99">
-        <v>2710.938</v>
+        <v>2841.091999999999</v>
       </c>
       <c r="F99">
-        <v>12624.938</v>
+        <v>12755.092</v>
       </c>
       <c r="G99">
         <v>643</v>
@@ -9530,45 +9530,45 @@
         <v>1486.333333333333</v>
       </c>
       <c r="M99">
-        <v>1853.3408984</v>
+        <v>2561.2224736</v>
       </c>
       <c r="N99">
-        <v>-367.007565066667</v>
+        <v>-1074.889140266667</v>
       </c>
       <c r="O99">
-        <v>-94.68795178720008</v>
+        <v>-277.3213981888</v>
       </c>
       <c r="P99">
-        <v>-272.3196132794669</v>
+        <v>-797.5677420778666</v>
       </c>
       <c r="Q99">
-        <v>-237.3196132794669</v>
+        <v>-762.5677420778666</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>0.9679243409019569</v>
+        <v>1.522388168399599</v>
       </c>
       <c r="T99">
-        <v>21.29617415477961</v>
+        <v>34.1013433810531</v>
       </c>
       <c r="U99">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V99">
-        <v>0.2069095870765358</v>
+        <v>0.1497230341966339</v>
       </c>
       <c r="W99">
-        <v>0.1164256726171645</v>
+        <v>0.1707356147333159</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y99">
-        <v>0.8019751437075032</v>
+        <v>0.5803218379714492</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9576,22 +9576,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.1977686658066416</v>
+        <v>0.1993186658066416</v>
       </c>
       <c r="C100">
-        <v>-7637.648055004642</v>
+        <v>-7801.659881481977</v>
       </c>
       <c r="D100">
-        <v>4474.443944995357</v>
+        <v>4440.586118518022</v>
       </c>
       <c r="E100">
-        <v>2841.091999999999</v>
+        <v>2971.245999999999</v>
       </c>
       <c r="F100">
-        <v>12755.092</v>
+        <v>12885.246</v>
       </c>
       <c r="G100">
         <v>643</v>
@@ -9612,37 +9612,37 @@
         <v>1486.333333333333</v>
       </c>
       <c r="M100">
-        <v>2561.2224736</v>
+        <v>2587.3573968</v>
       </c>
       <c r="N100">
-        <v>-1074.889140266667</v>
+        <v>-1101.024063466667</v>
       </c>
       <c r="O100">
-        <v>-277.3213981888</v>
+        <v>-284.0642083744</v>
       </c>
       <c r="P100">
-        <v>-797.5677420778666</v>
+        <v>-816.9598550922667</v>
       </c>
       <c r="Q100">
-        <v>-762.5677420778666</v>
+        <v>-781.9598550922667</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.522388168399599</v>
+        <v>2.998976336799198</v>
       </c>
       <c r="T100">
-        <v>34.1013433810531</v>
+        <v>68.2026867621062</v>
       </c>
       <c r="U100">
         <v>0.2008</v>
       </c>
       <c r="V100">
-        <v>0.1497230341966339</v>
+        <v>0.1482106803158598</v>
       </c>
       <c r="W100">
-        <v>0.1707356147333159</v>
+        <v>0.1710392953925753</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9650,91 +9650,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.5803218379714492</v>
+        <v>0.5744600012242627</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.1993186658066416</v>
-      </c>
-      <c r="C101">
-        <v>-7801.659881481977</v>
-      </c>
-      <c r="D101">
-        <v>4440.586118518022</v>
-      </c>
-      <c r="E101">
-        <v>2971.245999999999</v>
-      </c>
-      <c r="F101">
-        <v>12885.246</v>
-      </c>
-      <c r="G101">
-        <v>643</v>
-      </c>
-      <c r="H101">
-        <v>3101.4</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>1521.333333333333</v>
-      </c>
-      <c r="K101">
-        <v>35</v>
-      </c>
-      <c r="L101">
-        <v>1486.333333333333</v>
-      </c>
-      <c r="M101">
-        <v>2587.3573968</v>
-      </c>
-      <c r="N101">
-        <v>-1101.024063466667</v>
-      </c>
-      <c r="O101">
-        <v>-284.0642083744</v>
-      </c>
-      <c r="P101">
-        <v>-816.9598550922667</v>
-      </c>
-      <c r="Q101">
-        <v>-781.9598550922667</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>2.998976336799198</v>
-      </c>
-      <c r="T101">
-        <v>68.2026867621062</v>
-      </c>
-      <c r="U101">
-        <v>0.2008</v>
-      </c>
-      <c r="V101">
-        <v>0.1482106803158598</v>
-      </c>
-      <c r="W101">
-        <v>0.1710392953925753</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>C2/C</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.5744600012242627</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
